--- a/TSLA.xlsx
+++ b/TSLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zerrr\Desktop\FinModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622B6738-EE24-48F3-852B-548E787B83E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7850C238-9701-494E-98C4-1B64625C0CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
   <si>
     <t>Q122</t>
   </si>
@@ -341,7 +341,7 @@
     <numFmt numFmtId="172" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="173" formatCode="&quot;$&quot;#,##0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +376,12 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -404,26 +410,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,7 +482,7 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>22411</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>168088</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -504,7 +532,7 @@
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>62753</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>134470</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1041,7 +1069,7 @@
       <c r="N3" t="s">
         <v>59</v>
       </c>
-      <c r="O3" s="14" cm="1" vm="1">
+      <c r="O3" s="5" cm="1" vm="1">
         <f t="array" aca="1" ref="O3" ca="1">_xlfn.LET(_xlpm.p,_xlfn.STOCKHISTORY("TSLA",TODAY()-14,TODAY(),0,0,1),INDEX(_xlpm.p,ROWS(_xlpm.p),1))</f>
         <v>328.58</v>
       </c>
@@ -1050,7 +1078,7 @@
       <c r="N4" t="s">
         <v>49</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="3">
         <v>3949.5473940000002</v>
       </c>
     </row>
@@ -1058,7 +1086,7 @@
       <c r="N5" t="s">
         <v>60</v>
       </c>
-      <c r="O5" s="13">
+      <c r="O5" s="4">
         <f ca="1">O3*O4</f>
         <v>1297742.2827205199</v>
       </c>
@@ -1067,7 +1095,7 @@
       <c r="N6" t="s">
         <v>61</v>
       </c>
-      <c r="O6" s="13">
+      <c r="O6" s="4">
         <f>15219+28305</f>
         <v>43524</v>
       </c>
@@ -1076,7 +1104,7 @@
       <c r="N7" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="13">
+      <c r="O7" s="4">
         <f>1418+7924</f>
         <v>9342</v>
       </c>
@@ -1085,7 +1113,7 @@
       <c r="N8" t="s">
         <v>63</v>
       </c>
-      <c r="O8" s="13">
+      <c r="O8" s="4">
         <f ca="1">O5-O6+O7</f>
         <v>1263560.2827205199</v>
       </c>
@@ -1100,10 +1128,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="15" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.42578125" style="2" customWidth="1"/>
     <col min="3" max="26" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="9.140625" style="2"/>
@@ -1113,321 +1141,281 @@
     <col min="40" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="C3" s="3" t="s">
+    <row r="3" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AB3" s="10">
+      <c r="AB3" s="6">
         <v>2022</v>
       </c>
-      <c r="AC3" s="10">
+      <c r="AC3" s="6">
         <v>2023</v>
       </c>
-      <c r="AD3" s="10">
+      <c r="AD3" s="6">
         <v>2024</v>
       </c>
-      <c r="AE3" s="10">
+      <c r="AE3" s="6">
         <v>2025</v>
       </c>
-      <c r="AF3" s="10">
+      <c r="AF3" s="6">
         <v>2026</v>
       </c>
-      <c r="AG3" s="10">
+      <c r="AG3" s="6">
         <v>2027</v>
       </c>
-      <c r="AH3" s="10">
+      <c r="AH3" s="6">
         <v>2028</v>
       </c>
-      <c r="AI3" s="10">
+      <c r="AI3" s="6">
         <v>2029</v>
       </c>
-      <c r="AJ3" s="10">
+      <c r="AJ3" s="6">
         <v>2030</v>
       </c>
-      <c r="AK3" s="10">
+      <c r="AK3" s="6">
         <v>2031</v>
       </c>
       <c r="AM3" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>310048</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>254695</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>343830</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>405278</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>422875</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>466140</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>435059</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>484507</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <v>386810</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>443956</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <v>462890</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <v>495570</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="2">
         <v>336681</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="2">
         <v>384122</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
         <v>497099</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="2">
         <v>418227</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <v>358023</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4" s="2">
         <v>480126</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="2">
         <v>497099</v>
       </c>
-      <c r="V4" s="3">
+      <c r="V4" s="2">
         <v>418227</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W4" s="2">
         <v>358023</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="2">
         <v>480126</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Y4" s="2">
         <v>497099</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="Z4" s="2">
         <v>418227</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>0.84599999999999997</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>1.133</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>2.1</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>2.4620000000000002</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>3.8889999999999998</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>3.653</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>3.98</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>3.202</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>4.0529999999999999</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>9.4</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <v>6.9</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <v>11</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <v>10.4</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>9.6</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>12.5</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <v>14.2</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <v>8.8000000000000007</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="2">
         <v>13.5</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="2">
         <f t="shared" ref="U5:Z5" si="0">1.15*Q5</f>
         <v>14.374999999999998</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="2">
         <f t="shared" si="0"/>
         <v>16.329999999999998</v>
       </c>
-      <c r="W5" s="3">
+      <c r="W5" s="2">
         <f t="shared" si="0"/>
         <v>10.119999999999999</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="2">
         <f t="shared" si="0"/>
         <v>15.524999999999999</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="2">
         <f t="shared" si="0"/>
         <v>16.531249999999996</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="Z5" s="2">
         <f t="shared" si="0"/>
         <v>18.779499999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-    </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-    </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
@@ -1440,7 +1428,7 @@
       <c r="E8" s="2">
         <v>17785</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>20241</v>
       </c>
       <c r="G8" s="2">
@@ -1452,7 +1440,7 @@
       <c r="I8" s="2">
         <v>18582</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="7">
         <v>20630</v>
       </c>
       <c r="K8" s="2">
@@ -1464,7 +1452,7 @@
       <c r="M8" s="2">
         <v>18831</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="7">
         <v>18659</v>
       </c>
       <c r="O8" s="2">
@@ -1476,7 +1464,7 @@
       <c r="Q8" s="2">
         <v>20359</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="7">
         <v>16750</v>
       </c>
       <c r="S8" s="2">
@@ -1486,7 +1474,7 @@
         <v>20006</v>
       </c>
       <c r="U8" s="2">
-        <f t="shared" ref="U8:Z8" si="1">U4*U39/1000000</f>
+        <f t="shared" ref="U8:Z8" si="1">U4*U41/1000000</f>
         <v>20359.000000000004</v>
       </c>
       <c r="V8" s="2">
@@ -1550,7 +1538,7 @@
         <v>88231.167675000033</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
@@ -1563,7 +1551,7 @@
       <c r="E9" s="2">
         <v>621</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>599</v>
       </c>
       <c r="G9" s="2">
@@ -1575,7 +1563,7 @@
       <c r="I9" s="2">
         <v>489</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="7">
         <v>500</v>
       </c>
       <c r="K9" s="2">
@@ -1587,7 +1575,7 @@
       <c r="M9" s="2">
         <v>446</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="7">
         <v>447</v>
       </c>
       <c r="O9" s="2">
@@ -1599,7 +1587,7 @@
       <c r="Q9" s="2">
         <v>429</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="7">
         <v>397</v>
       </c>
       <c r="S9" s="2">
@@ -1673,7 +1661,7 @@
         <v>1909.5603187500008</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
@@ -1686,7 +1674,7 @@
       <c r="E10" s="2">
         <v>286</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>467</v>
       </c>
       <c r="G10" s="2">
@@ -1698,7 +1686,7 @@
       <c r="I10" s="2">
         <v>554</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="7">
         <v>433</v>
       </c>
       <c r="K10" s="2">
@@ -1710,7 +1698,7 @@
       <c r="M10" s="2">
         <v>739</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="7">
         <v>692</v>
       </c>
       <c r="O10" s="2">
@@ -1722,7 +1710,7 @@
       <c r="Q10" s="2">
         <v>417</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="7">
         <v>546</v>
       </c>
       <c r="S10" s="2">
@@ -1796,7 +1784,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
@@ -1809,7 +1797,7 @@
       <c r="E11" s="2">
         <v>1117</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>1310</v>
       </c>
       <c r="G11" s="2">
@@ -1821,7 +1809,7 @@
       <c r="I11" s="2">
         <v>1559</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="7">
         <v>1438</v>
       </c>
       <c r="K11" s="2">
@@ -1833,7 +1821,7 @@
       <c r="M11" s="2">
         <v>2376</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="7">
         <v>3061</v>
       </c>
       <c r="O11" s="2">
@@ -1845,7 +1833,7 @@
       <c r="Q11" s="2">
         <v>3415</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="7">
         <v>3837</v>
       </c>
       <c r="S11" s="2">
@@ -1855,11 +1843,11 @@
         <v>3139</v>
       </c>
       <c r="U11" s="2">
-        <f>U5*U40/1000000</f>
+        <f>U5*U42/1000000</f>
         <v>3927.2499999999995</v>
       </c>
       <c r="V11" s="2">
-        <f t="shared" ref="V11:Z11" si="11">V5*V40/1000000</f>
+        <f t="shared" ref="V11:Z11" si="11">V5*V42/1000000</f>
         <v>4412.5499999999993</v>
       </c>
       <c r="W11" s="2">
@@ -1919,7 +1907,7 @@
         <v>23381.413462</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
@@ -1932,7 +1920,7 @@
       <c r="E12" s="2">
         <v>1645</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>1701</v>
       </c>
       <c r="G12" s="2">
@@ -1944,7 +1932,7 @@
       <c r="I12" s="2">
         <v>2166</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="7">
         <v>2166</v>
       </c>
       <c r="K12" s="2">
@@ -1956,7 +1944,7 @@
       <c r="M12" s="2">
         <v>2790</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="7">
         <v>2848</v>
       </c>
       <c r="O12" s="2">
@@ -1968,7 +1956,7 @@
       <c r="Q12" s="2">
         <v>3475</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="7">
         <v>3371</v>
       </c>
       <c r="S12" s="2">
@@ -2042,8 +2030,8 @@
         <v>32581.773944593733</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+    <row r="13" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2">
@@ -2183,7 +2171,7 @@
         <v>275925</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>30</v>
       </c>
@@ -2196,7 +2184,7 @@
       <c r="E14" s="2">
         <v>13099</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>15433</v>
       </c>
       <c r="G14" s="2">
@@ -2208,7 +2196,7 @@
       <c r="I14" s="2">
         <v>15656</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="7">
         <v>17202</v>
       </c>
       <c r="K14" s="2">
@@ -2220,7 +2208,7 @@
       <c r="M14" s="2">
         <v>15743</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="7">
         <v>16268</v>
       </c>
       <c r="O14" s="2">
@@ -2232,7 +2220,7 @@
       <c r="Q14" s="2">
         <v>17365</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="7">
         <v>13874</v>
       </c>
       <c r="S14" s="2">
@@ -2242,11 +2230,11 @@
         <v>16866</v>
       </c>
       <c r="U14" s="2">
-        <f>U8*(1-U42)</f>
+        <f>U8*(1-U44)</f>
         <v>16997.938320224453</v>
       </c>
       <c r="V14" s="2">
-        <f t="shared" ref="V14:Z14" si="19">V8*(1-V42)</f>
+        <f t="shared" ref="V14:Z14" si="19">V8*(1-V44)</f>
         <v>13984.747132165608</v>
       </c>
       <c r="W14" s="2">
@@ -2306,7 +2294,7 @@
         <v>176590</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>31</v>
       </c>
@@ -2319,7 +2307,7 @@
       <c r="E15" s="2">
         <v>381</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>352</v>
       </c>
       <c r="G15" s="2">
@@ -2331,7 +2319,7 @@
       <c r="I15" s="2">
         <v>301</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="7">
         <v>296</v>
       </c>
       <c r="K15" s="2">
@@ -2343,7 +2331,7 @@
       <c r="M15" s="2">
         <v>247</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="7">
         <v>242</v>
       </c>
       <c r="O15" s="2">
@@ -2355,7 +2343,7 @@
       <c r="Q15" s="2">
         <v>225</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="7">
         <v>206</v>
       </c>
       <c r="S15" s="2">
@@ -2365,11 +2353,11 @@
         <v>187</v>
       </c>
       <c r="U15" s="2">
-        <f>U9*(1-U43)</f>
+        <f>U9*(1-U45)</f>
         <v>222.1725761334304</v>
       </c>
       <c r="V15" s="2">
-        <f t="shared" ref="V15:Z15" si="20">V9*(1-V43)</f>
+        <f t="shared" ref="V15:Z15" si="20">V9*(1-V45)</f>
         <v>205.60026276217218</v>
       </c>
       <c r="W15" s="2">
@@ -2377,7 +2365,7 @@
         <v>197.31410607654308</v>
       </c>
       <c r="X15" s="2">
-        <f>X9*(1-X43)</f>
+        <f>X9*(1-X45)</f>
         <v>188.51006459806214</v>
       </c>
       <c r="Y15" s="2">
@@ -2429,7 +2417,7 @@
         <v>3780</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
@@ -2442,7 +2430,7 @@
       <c r="E16" s="2">
         <v>1013</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>1151</v>
       </c>
       <c r="G16" s="2">
@@ -2454,7 +2442,7 @@
       <c r="I16" s="2">
         <v>1178</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="7">
         <v>1124</v>
       </c>
       <c r="K16" s="2">
@@ -2466,7 +2454,7 @@
       <c r="M16" s="2">
         <v>1651</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="7">
         <v>2289</v>
       </c>
       <c r="O16" s="2">
@@ -2478,7 +2466,7 @@
       <c r="Q16" s="2">
         <v>2342</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="7">
         <v>2739</v>
       </c>
       <c r="S16" s="2">
@@ -2488,11 +2476,11 @@
         <v>2499</v>
       </c>
       <c r="U16" s="2">
-        <f>U11*(1-U44)</f>
+        <f>U11*(1-U46)</f>
         <v>2749.4691600114675</v>
       </c>
       <c r="V16" s="2">
-        <f t="shared" ref="V16:Z16" si="21">V11*(1-V44)</f>
+        <f t="shared" ref="V16:Z16" si="21">V11*(1-V46)</f>
         <v>3089.2278673393853</v>
       </c>
       <c r="W16" s="2">
@@ -2552,7 +2540,7 @@
         <v>15961</v>
       </c>
     </row>
-    <row r="17" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
@@ -2565,7 +2553,7 @@
       <c r="E17" s="2">
         <v>1579</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>1605</v>
       </c>
       <c r="G17" s="2">
@@ -2577,7 +2565,7 @@
       <c r="I17" s="2">
         <v>2037</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="7">
         <v>2107</v>
       </c>
       <c r="K17" s="2">
@@ -2589,7 +2577,7 @@
       <c r="M17" s="2">
         <v>2544</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="7">
         <v>2729</v>
       </c>
       <c r="O17" s="2">
@@ -2601,7 +2589,7 @@
       <c r="Q17" s="2">
         <v>3109</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="7">
         <v>3073</v>
       </c>
       <c r="S17" s="2">
@@ -2611,15 +2599,15 @@
         <v>3933</v>
       </c>
       <c r="U17" s="2">
-        <f>U12*(1-U45)</f>
+        <f>U12*(1-U47)</f>
         <v>3355.4985285159487</v>
       </c>
       <c r="V17" s="2">
-        <f>V12*(1-V45)</f>
+        <f>V12*(1-V47)</f>
         <v>3408.9487142901653</v>
       </c>
       <c r="W17" s="2">
-        <f t="shared" ref="W17:Z17" si="22">W12*(1-W45)</f>
+        <f t="shared" ref="W17:Z17" si="22">W12*(1-W47)</f>
         <v>3752.4415548118764</v>
       </c>
       <c r="X17" s="2">
@@ -2675,8 +2663,8 @@
         <v>23631</v>
       </c>
     </row>
-    <row r="18" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C18" s="2">
@@ -2816,8 +2804,8 @@
         <v>219962</v>
       </c>
     </row>
-    <row r="19" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+    <row r="19" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="2">
@@ -2957,7 +2945,7 @@
         <v>55963</v>
       </c>
     </row>
-    <row r="20" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>36</v>
       </c>
@@ -2970,7 +2958,7 @@
       <c r="E20" s="2">
         <v>733</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>810</v>
       </c>
       <c r="G20" s="2">
@@ -2982,7 +2970,7 @@
       <c r="I20" s="2">
         <v>1161</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="7">
         <v>1094</v>
       </c>
       <c r="K20" s="2">
@@ -2994,7 +2982,7 @@
       <c r="M20" s="2">
         <v>1039</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="7">
         <v>1276</v>
       </c>
       <c r="O20" s="2">
@@ -3006,7 +2994,7 @@
       <c r="Q20" s="2">
         <v>1630</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="7">
         <v>1783</v>
       </c>
       <c r="S20" s="2">
@@ -3016,11 +3004,11 @@
         <v>2371</v>
       </c>
       <c r="U20" s="2">
-        <f>U46*U13</f>
+        <f>U48*U13</f>
         <v>2185.0421866637957</v>
       </c>
       <c r="V20" s="2">
-        <f t="shared" ref="V20:Z20" si="27">V46*V13</f>
+        <f t="shared" ref="V20:Z20" si="27">V48*V13</f>
         <v>1938.9711444501909</v>
       </c>
       <c r="W20" s="2">
@@ -3080,7 +3068,7 @@
         <v>11584</v>
       </c>
     </row>
-    <row r="21" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>37</v>
       </c>
@@ -3093,7 +3081,7 @@
       <c r="E21" s="2">
         <v>961</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="7">
         <v>1032</v>
       </c>
       <c r="G21" s="2">
@@ -3105,7 +3093,7 @@
       <c r="I21" s="2">
         <v>1253</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="7">
         <v>1280</v>
       </c>
       <c r="K21" s="2">
@@ -3117,7 +3105,7 @@
       <c r="M21" s="2">
         <v>1186</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="7">
         <v>1313</v>
       </c>
       <c r="O21" s="2">
@@ -3129,7 +3117,7 @@
       <c r="Q21" s="2">
         <v>1562</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="7">
         <v>1655</v>
       </c>
       <c r="S21" s="2">
@@ -3139,11 +3127,11 @@
         <v>1982</v>
       </c>
       <c r="U21" s="2">
-        <f>U47*U13</f>
+        <f>U49*U13</f>
         <v>1993.1983082632028</v>
       </c>
       <c r="V21" s="2">
-        <f t="shared" ref="V21:Z21" si="28">V47*V13</f>
+        <f t="shared" ref="V21:Z21" si="28">V49*V13</f>
         <v>1768.731985349051</v>
       </c>
       <c r="W21" s="2">
@@ -3203,17 +3191,17 @@
         <v>13896</v>
       </c>
     </row>
-    <row r="22" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="2">
         <v>142</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="7">
         <v>34</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="7">
         <v>0</v>
       </c>
       <c r="L22" s="2">
@@ -3222,7 +3210,7 @@
       <c r="M22" s="2">
         <v>55</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="7">
         <v>7</v>
       </c>
       <c r="O22" s="2">
@@ -3231,7 +3219,7 @@
       <c r="Q22" s="2">
         <v>238</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="7">
         <v>162</v>
       </c>
       <c r="T22" s="2">
@@ -3296,8 +3284,8 @@
         <v>860</v>
       </c>
     </row>
-    <row r="23" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
+    <row r="23" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="2">
@@ -3437,7 +3425,7 @@
         <v>26340</v>
       </c>
     </row>
-    <row r="24" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>40</v>
       </c>
@@ -3578,7 +3566,7 @@
         <v>29623</v>
       </c>
     </row>
-    <row r="25" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>41</v>
       </c>
@@ -3591,7 +3579,7 @@
       <c r="E25" s="2">
         <v>86</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="7">
         <v>157</v>
       </c>
       <c r="G25" s="2">
@@ -3603,7 +3591,7 @@
       <c r="I25" s="2">
         <v>282</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="7">
         <v>333</v>
       </c>
       <c r="K25" s="2">
@@ -3615,7 +3603,7 @@
       <c r="M25" s="2">
         <v>429</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="7">
         <v>442</v>
       </c>
       <c r="O25" s="2">
@@ -3627,7 +3615,7 @@
       <c r="Q25" s="2">
         <v>439</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="7">
         <v>449</v>
       </c>
       <c r="S25" s="2">
@@ -3701,7 +3689,7 @@
         <v>2932</v>
       </c>
     </row>
-    <row r="26" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>42</v>
       </c>
@@ -3714,7 +3702,7 @@
       <c r="E26" s="2">
         <v>-53</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="7">
         <v>-33</v>
       </c>
       <c r="G26" s="2">
@@ -3726,7 +3714,7 @@
       <c r="I26" s="2">
         <v>-38</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="7">
         <v>-61</v>
       </c>
       <c r="K26" s="2">
@@ -3738,7 +3726,7 @@
       <c r="M26" s="2">
         <v>-92</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="7">
         <v>-96</v>
       </c>
       <c r="O26" s="2">
@@ -3750,7 +3738,7 @@
       <c r="Q26" s="2">
         <v>-76</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="7">
         <v>-85</v>
       </c>
       <c r="S26" s="2">
@@ -3824,7 +3812,7 @@
         <v>-697</v>
       </c>
     </row>
-    <row r="27" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>43</v>
       </c>
@@ -3837,7 +3825,7 @@
       <c r="E27" s="2">
         <v>-85</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="7">
         <v>-42</v>
       </c>
       <c r="G27" s="2">
@@ -3849,7 +3837,7 @@
       <c r="I27" s="2">
         <v>37</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="7">
         <v>-145</v>
       </c>
       <c r="K27" s="2">
@@ -3861,7 +3849,7 @@
       <c r="M27" s="2">
         <v>-263</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="7">
         <v>830</v>
       </c>
       <c r="O27" s="2">
@@ -3873,7 +3861,7 @@
       <c r="Q27" s="2">
         <v>-28</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="7">
         <v>-592</v>
       </c>
       <c r="S27" s="2">
@@ -3941,8 +3929,8 @@
         <v>824</v>
       </c>
     </row>
-    <row r="28" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
+    <row r="28" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="2">
@@ -4082,7 +4070,7 @@
         <v>32682</v>
       </c>
     </row>
-    <row r="29" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
@@ -4095,7 +4083,7 @@
       <c r="E29" s="2">
         <v>305</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="7">
         <v>276</v>
       </c>
       <c r="G29" s="2">
@@ -4107,7 +4095,7 @@
       <c r="I29" s="2">
         <v>167</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="7">
         <v>-5752</v>
       </c>
       <c r="K29" s="2">
@@ -4119,7 +4107,7 @@
       <c r="M29" s="2">
         <v>602</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="7">
         <v>433</v>
       </c>
       <c r="O29" s="2">
@@ -4131,7 +4119,7 @@
       <c r="Q29" s="2">
         <v>570</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="7">
         <v>325</v>
       </c>
       <c r="S29" s="2">
@@ -4141,11 +4129,11 @@
         <v>201</v>
       </c>
       <c r="U29" s="2">
-        <f>U28*U49</f>
+        <f>U28*U51</f>
         <v>512.70012524213905</v>
       </c>
       <c r="V29" s="2">
-        <f t="shared" ref="V29:Z29" si="42">V28*V49</f>
+        <f t="shared" ref="V29:Z29" si="42">V28*V51</f>
         <v>468.08379913587083</v>
       </c>
       <c r="W29" s="2">
@@ -4205,8 +4193,8 @@
         <v>-2032</v>
       </c>
     </row>
-    <row r="30" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B30" s="4" t="s">
+    <row r="30" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C30" s="2">
@@ -4346,7 +4334,7 @@
         <v>34714</v>
       </c>
     </row>
-    <row r="31" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>47</v>
       </c>
@@ -4359,7 +4347,7 @@
       <c r="E31" s="2">
         <v>39</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="7">
         <v>20</v>
       </c>
       <c r="G31" s="2">
@@ -4371,7 +4359,7 @@
       <c r="I31" s="2">
         <v>25</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="7">
         <v>15</v>
       </c>
       <c r="K31" s="2">
@@ -4383,7 +4371,7 @@
       <c r="M31" s="2">
         <v>16</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="7">
         <v>15</v>
       </c>
       <c r="O31" s="2">
@@ -4395,7 +4383,7 @@
       <c r="Q31" s="2">
         <v>16</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="7">
         <v>16</v>
       </c>
       <c r="S31" s="2">
@@ -4463,7 +4451,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>48</v>
       </c>
@@ -4603,8 +4591,8 @@
         <v>34644</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="B33" s="4" t="s">
+    <row r="33" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
         <v>80</v>
       </c>
       <c r="C33" s="2">
@@ -4744,7 +4732,7 @@
         <v>10.702502316960148</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>49</v>
       </c>
@@ -4857,8 +4845,8 @@
         <v>3237</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="B35" s="4" t="s">
+    <row r="35" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C35" s="2">
@@ -4998,7 +4986,7 @@
         <v>9.7864406779661017</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>51</v>
       </c>
@@ -5111,1929 +5099,1944 @@
         <v>3540</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:37" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:37" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="8" t="s">
+    <row r="37" spans="1:37" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:37" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+    </row>
+    <row r="40" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="9"/>
+    </row>
+    <row r="41" spans="1:37" s="2" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C41" s="2">
         <f>(C8/C4)*1000000</f>
         <v>50037.413561771085</v>
       </c>
-      <c r="D39" s="2">
-        <f t="shared" ref="D39:T39" si="58">(D8/D4)*1000000</f>
+      <c r="D41" s="2">
+        <f t="shared" ref="D41:T41" si="58">(D8/D4)*1000000</f>
         <v>53672.039105596887</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E41" s="2">
         <f t="shared" si="58"/>
         <v>51726.143733821948</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F41" s="2">
         <f t="shared" si="58"/>
         <v>49943.49557587631</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G41" s="2">
         <f t="shared" si="58"/>
         <v>44642.033697901272</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H41" s="2">
         <f t="shared" si="58"/>
         <v>43804.436435405674</v>
       </c>
-      <c r="I39" s="2">
+      <c r="I41" s="2">
         <f t="shared" si="58"/>
         <v>42711.448332295164</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J41" s="2">
         <f t="shared" si="58"/>
         <v>42579.364178432923</v>
       </c>
-      <c r="K39" s="2">
+      <c r="K41" s="2">
         <f t="shared" si="58"/>
         <v>42553.191489361699</v>
       </c>
-      <c r="L39" s="2">
+      <c r="L41" s="2">
         <f t="shared" si="58"/>
         <v>41738.370469145593</v>
       </c>
-      <c r="M39" s="2">
+      <c r="M41" s="2">
         <f t="shared" si="58"/>
         <v>40681.371384130136</v>
       </c>
-      <c r="N39" s="2">
+      <c r="N41" s="2">
         <f t="shared" si="58"/>
         <v>37651.59311499889</v>
       </c>
-      <c r="O39" s="2">
+      <c r="O41" s="2">
         <f t="shared" si="58"/>
         <v>38389.454706383789</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P41" s="2">
         <f t="shared" si="58"/>
         <v>41098.921696752594</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q41" s="2">
         <f t="shared" si="58"/>
         <v>40955.624533543625</v>
       </c>
-      <c r="R39" s="2">
+      <c r="R41" s="2">
         <f t="shared" si="58"/>
         <v>40050.020682547998</v>
       </c>
-      <c r="S39" s="2">
+      <c r="S41" s="2">
         <f t="shared" si="58"/>
         <v>43217.893822463913</v>
       </c>
-      <c r="T39" s="2">
+      <c r="T41" s="2">
         <f t="shared" si="58"/>
         <v>41668.228756618053</v>
       </c>
-      <c r="U39" s="2">
-        <f t="shared" ref="U39:Z39" si="59">Q39</f>
+      <c r="U41" s="2">
+        <f t="shared" ref="U41:Z41" si="59">Q41</f>
         <v>40955.624533543625</v>
       </c>
-      <c r="V39" s="2">
+      <c r="V41" s="2">
         <f t="shared" si="59"/>
         <v>40050.020682547998</v>
       </c>
-      <c r="W39" s="2">
+      <c r="W41" s="2">
         <f t="shared" si="59"/>
         <v>43217.893822463913</v>
       </c>
-      <c r="X39" s="2">
+      <c r="X41" s="2">
         <f t="shared" si="59"/>
         <v>41668.228756618053</v>
       </c>
-      <c r="Y39" s="2">
+      <c r="Y41" s="2">
         <f t="shared" si="59"/>
         <v>40955.624533543625</v>
       </c>
-      <c r="Z39" s="2">
+      <c r="Z41" s="2">
         <f t="shared" si="59"/>
         <v>40050.020682547998</v>
       </c>
-      <c r="AB39" s="11">
+      <c r="AB41" s="11">
         <f>AB8/SUM(C4:F4)*1000000</f>
         <v>51154.963538483433</v>
       </c>
-      <c r="AC39" s="11">
+      <c r="AC41" s="11">
         <f>AC8/SUM(G4:J4)*1000000</f>
         <v>43409.169951470241</v>
       </c>
-      <c r="AD39" s="11">
+      <c r="AD41" s="11">
         <f>AD8/SUM(K4:N4)*1000000</f>
         <v>40509.136352814006</v>
       </c>
-      <c r="AE39" s="11">
+      <c r="AE41" s="11">
         <f>AE8/SUM(O4:R4)*1000000</f>
         <v>40229.712938282988</v>
       </c>
-      <c r="AF39" s="11">
+      <c r="AF41" s="11">
         <f>AF8/SUM(S4:V4)*1000000</f>
         <v>41396.65521321947</v>
       </c>
-      <c r="AG39" s="11">
+      <c r="AG41" s="11">
         <f>AG8/SUM(W4:Z4)*1000000</f>
         <v>41396.65521321947</v>
       </c>
-      <c r="AH39" s="11">
-        <f t="shared" ref="AH39:AK40" si="60">AG39</f>
+      <c r="AH41" s="11">
+        <f t="shared" ref="AH41:AK42" si="60">AG41</f>
         <v>41396.65521321947</v>
       </c>
-      <c r="AI39" s="11">
+      <c r="AI41" s="11">
         <f t="shared" si="60"/>
         <v>41396.65521321947</v>
       </c>
-      <c r="AJ39" s="11">
+      <c r="AJ41" s="11">
         <f t="shared" si="60"/>
         <v>41396.65521321947</v>
       </c>
-      <c r="AK39" s="11">
+      <c r="AK41" s="11">
         <f t="shared" si="60"/>
         <v>41396.65521321947</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
+    <row r="42" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C42" s="2">
         <f>(C11/C5)*1000000</f>
         <v>728132387.70685589</v>
       </c>
-      <c r="D40" s="2">
-        <f t="shared" ref="D40:T40" si="61">(D11/D5)*1000000</f>
+      <c r="D42" s="2">
+        <f t="shared" ref="D42:T42" si="61">(D11/D5)*1000000</f>
         <v>764342453.66284204</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E42" s="2">
         <f t="shared" si="61"/>
         <v>531904761.90476191</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F42" s="2">
         <f t="shared" si="61"/>
         <v>532087733.54995936</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G42" s="2">
         <f t="shared" si="61"/>
         <v>393160195.42298794</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H42" s="2">
         <f t="shared" si="61"/>
         <v>413085135.50506431</v>
       </c>
-      <c r="I40" s="2">
+      <c r="I42" s="2">
         <f t="shared" si="61"/>
         <v>391708542.71356785</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J42" s="2">
         <f t="shared" si="61"/>
         <v>449094316.05246723</v>
       </c>
-      <c r="K40" s="2">
+      <c r="K42" s="2">
         <f t="shared" si="61"/>
         <v>403404885.27017027</v>
       </c>
-      <c r="L40" s="2">
+      <c r="L42" s="2">
         <f t="shared" si="61"/>
         <v>320638297.87234038</v>
       </c>
-      <c r="M40" s="2">
+      <c r="M42" s="2">
         <f t="shared" si="61"/>
         <v>344347826.0869565</v>
       </c>
-      <c r="N40" s="2">
+      <c r="N42" s="2">
         <f t="shared" si="61"/>
         <v>278272727.27272725</v>
       </c>
-      <c r="O40" s="2">
+      <c r="O42" s="2">
         <f t="shared" si="61"/>
         <v>262500000</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P42" s="2">
         <f t="shared" si="61"/>
         <v>290520833.33333337</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q42" s="2">
         <f t="shared" si="61"/>
         <v>273200000</v>
       </c>
-      <c r="R40" s="2">
+      <c r="R42" s="2">
         <f t="shared" si="61"/>
         <v>270211267.6056338</v>
       </c>
-      <c r="S40" s="2">
+      <c r="S42" s="2">
         <f t="shared" si="61"/>
         <v>273636363.63636363</v>
       </c>
-      <c r="T40" s="2">
+      <c r="T42" s="2">
         <f t="shared" si="61"/>
         <v>232518518.51851851</v>
       </c>
-      <c r="U40" s="2">
-        <f>Q40</f>
+      <c r="U42" s="2">
+        <f>Q42</f>
         <v>273200000</v>
       </c>
-      <c r="V40" s="2">
-        <f t="shared" ref="V40:X40" si="62">R40</f>
+      <c r="V42" s="2">
+        <f t="shared" ref="V42:X42" si="62">R42</f>
         <v>270211267.6056338</v>
       </c>
-      <c r="W40" s="2">
+      <c r="W42" s="2">
         <f t="shared" si="62"/>
         <v>273636363.63636363</v>
       </c>
-      <c r="X40" s="2">
+      <c r="X42" s="2">
         <f t="shared" si="62"/>
         <v>232518518.51851851</v>
       </c>
-      <c r="Y40" s="2">
-        <f>U40</f>
+      <c r="Y42" s="2">
+        <f>U42</f>
         <v>273200000</v>
       </c>
-      <c r="Z40" s="2">
-        <f>V40</f>
+      <c r="Z42" s="2">
+        <f>V42</f>
         <v>270211267.6056338</v>
       </c>
-      <c r="AB40" s="11">
+      <c r="AB42" s="11">
         <f>AB11/SUM(C5:F5)*1000000</f>
         <v>597615043.57131934</v>
       </c>
-      <c r="AC40" s="11">
+      <c r="AC42" s="11">
         <f>AC11/SUM(G5:J5)*1000000</f>
         <v>409875033.95816356</v>
       </c>
-      <c r="AD40" s="11">
+      <c r="AD42" s="11">
         <f>AD11/SUM(K5:N5)*1000000</f>
         <v>321691704.14314419</v>
       </c>
-      <c r="AE40" s="11">
+      <c r="AE42" s="11">
         <f>AE11/SUM(O5:R5)*1000000</f>
         <v>273468950.74946463</v>
       </c>
-      <c r="AF40" s="11">
+      <c r="AF42" s="11">
         <f>AF11/SUM(S5:V5)*1000000</f>
         <v>261990378.26620135</v>
       </c>
-      <c r="AG40" s="11">
+      <c r="AG42" s="11">
         <f>AG11/SUM(W5:Z5)*1000000</f>
         <v>261990378.26620129</v>
       </c>
-      <c r="AH40" s="11">
+      <c r="AH42" s="11">
         <f t="shared" si="60"/>
         <v>261990378.26620129</v>
       </c>
-      <c r="AI40" s="11">
+      <c r="AI42" s="11">
         <f t="shared" si="60"/>
         <v>261990378.26620129</v>
       </c>
-      <c r="AJ40" s="11">
+      <c r="AJ42" s="11">
         <f t="shared" si="60"/>
         <v>261990378.26620129</v>
       </c>
-      <c r="AK40" s="11">
+      <c r="AK42" s="11">
         <f t="shared" si="60"/>
         <v>261990378.26620129</v>
       </c>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+    <row r="44" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C44" s="12">
         <f>(C8-C14)/C8</f>
         <v>0.29650638133298957</v>
       </c>
-      <c r="D42" s="9">
-        <f t="shared" ref="D42:T42" si="63">(D8-D14)/D8</f>
+      <c r="D44" s="12">
+        <f t="shared" ref="D44:T44" si="63">(D8-D14)/D8</f>
         <v>0.25727871250914414</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E44" s="12">
         <f t="shared" si="63"/>
         <v>0.26348046106269329</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F44" s="12">
         <f t="shared" si="63"/>
         <v>0.23753767106368262</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G44" s="12">
         <f t="shared" si="63"/>
         <v>0.1830702404915775</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H44" s="12">
         <f t="shared" si="63"/>
         <v>0.17522895342573094</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I44" s="12">
         <f t="shared" si="63"/>
         <v>0.15746421267893659</v>
       </c>
-      <c r="J42" s="9">
+      <c r="J44" s="12">
         <f t="shared" si="63"/>
         <v>0.16616577799321378</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K44" s="12">
         <f t="shared" si="63"/>
         <v>0.15571081409477522</v>
       </c>
-      <c r="L42" s="9">
+      <c r="L44" s="12">
         <f t="shared" si="63"/>
         <v>0.13858607663248787</v>
       </c>
-      <c r="M42" s="9">
+      <c r="M44" s="12">
         <f t="shared" si="63"/>
         <v>0.16398491848547608</v>
       </c>
-      <c r="N42" s="9">
+      <c r="N44" s="12">
         <f t="shared" si="63"/>
         <v>0.12814191542955142</v>
       </c>
-      <c r="O42" s="9">
+      <c r="O44" s="12">
         <f t="shared" si="63"/>
         <v>0.1132688588007737</v>
       </c>
-      <c r="P42" s="9">
+      <c r="P44" s="12">
         <f t="shared" si="63"/>
         <v>0.14062203078482297</v>
       </c>
-      <c r="Q42" s="9">
+      <c r="Q44" s="12">
         <f t="shared" si="63"/>
         <v>0.14706026818606022</v>
       </c>
-      <c r="R42" s="9">
+      <c r="R44" s="12">
         <f>(R8-R14)/R8</f>
         <v>0.17170149253731343</v>
       </c>
-      <c r="S42" s="9">
+      <c r="S44" s="12">
         <f t="shared" si="63"/>
         <v>0.18464421896206296</v>
       </c>
-      <c r="T42" s="9">
+      <c r="T44" s="12">
         <f t="shared" si="63"/>
         <v>0.15695291412576226</v>
       </c>
-      <c r="U42" s="9">
-        <f>AVERAGE(Q42:T42)</f>
+      <c r="U44" s="12">
+        <f>AVERAGE(Q44:T44)</f>
         <v>0.16508972345279974</v>
       </c>
-      <c r="V42" s="9">
-        <f>U42</f>
+      <c r="V44" s="12">
+        <f>U44</f>
         <v>0.16508972345279974</v>
       </c>
-      <c r="W42" s="9">
-        <f t="shared" ref="W42:Y42" si="64">V42</f>
+      <c r="W44" s="12">
+        <f t="shared" ref="W44:Y44" si="64">V44</f>
         <v>0.16508972345279974</v>
       </c>
-      <c r="X42" s="9">
+      <c r="X44" s="12">
         <f t="shared" si="64"/>
         <v>0.16508972345279974</v>
       </c>
-      <c r="Y42" s="9">
+      <c r="Y44" s="12">
         <f t="shared" si="64"/>
         <v>0.16508972345279974</v>
       </c>
-      <c r="Z42" s="9">
-        <f>Y42</f>
+      <c r="Z44" s="12">
+        <f>Y44</f>
         <v>0.16508972345279974</v>
       </c>
-      <c r="AB42" s="12">
-        <f t="shared" ref="AB42:AK43" si="65">(AB8-AB14)/AB8</f>
+      <c r="AB44" s="13">
+        <f>(AB8-AB14)/AB8</f>
         <v>0.26202945990180032</v>
       </c>
-      <c r="AC42" s="12">
-        <f t="shared" si="65"/>
+      <c r="AC44" s="13">
+        <f>(AC8-AC14)/AC8</f>
         <v>0.17052821969455731</v>
       </c>
-      <c r="AD42" s="12">
-        <f t="shared" si="65"/>
+      <c r="AD44" s="13">
+        <f>(AD8-AD14)/AD8</f>
         <v>0.14638520971302429</v>
       </c>
-      <c r="AE42" s="12">
-        <f t="shared" si="65"/>
+      <c r="AE44" s="13">
+        <f>(AE8-AE14)/AE8</f>
         <v>0.14515124352410325</v>
       </c>
-      <c r="AF42" s="12">
-        <f t="shared" si="65"/>
+      <c r="AF44" s="13">
+        <f>(AF8-AF14)/AF8</f>
         <v>0.16701540953890376</v>
       </c>
-      <c r="AG42" s="12">
-        <f t="shared" si="65"/>
+      <c r="AG44" s="13">
+        <f>(AG8-AG14)/AG8</f>
         <v>0.16508972345279968</v>
       </c>
-      <c r="AH42" s="12">
-        <f t="shared" si="65"/>
+      <c r="AH44" s="13">
+        <f>(AH8-AH14)/AH8</f>
         <v>0.37434364797285985</v>
       </c>
-      <c r="AI42" s="12">
-        <f t="shared" si="65"/>
+      <c r="AI44" s="13">
+        <f>(AI8-AI14)/AI8</f>
         <v>-6.9152494785909525E-3</v>
       </c>
-      <c r="AJ42" s="12">
-        <f t="shared" si="65"/>
+      <c r="AJ44" s="13">
+        <f>(AJ8-AJ14)/AJ8</f>
         <v>-0.53165812093253406</v>
       </c>
-      <c r="AK42" s="12">
-        <f t="shared" si="65"/>
+      <c r="AK44" s="13">
+        <f>(AK8-AK14)/AK8</f>
         <v>-1.0014469337011405</v>
       </c>
     </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
+    <row r="45" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C45" s="12">
         <f>(C9-C15)/C9</f>
         <v>0.38922155688622756</v>
       </c>
-      <c r="D43" s="9">
-        <f t="shared" ref="D43:T43" si="66">(D9-D15)/D9</f>
+      <c r="D45" s="12">
+        <f t="shared" ref="D45:T45" si="65">(D9-D15)/D9</f>
         <v>0.37414965986394561</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.38647342995169082</v>
+      </c>
+      <c r="F45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.41235392320534225</v>
+      </c>
+      <c r="G45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.40957446808510639</v>
+      </c>
+      <c r="H45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.40388007054673719</v>
+      </c>
+      <c r="I45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.38445807770961143</v>
+      </c>
+      <c r="J45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="K45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.43487394957983194</v>
+      </c>
+      <c r="L45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.46506550218340609</v>
+      </c>
+      <c r="M45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.4461883408071749</v>
+      </c>
+      <c r="N45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.45861297539149887</v>
+      </c>
+      <c r="O45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.46532438478747201</v>
+      </c>
+      <c r="P45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.48063781321184512</v>
+      </c>
+      <c r="Q45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.47552447552447552</v>
+      </c>
+      <c r="R45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.48110831234256929</v>
+      </c>
+      <c r="S45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.48556430446194226</v>
+      </c>
+      <c r="T45" s="12">
+        <f t="shared" si="65"/>
+        <v>0.48626373626373626</v>
+      </c>
+      <c r="U45" s="12">
+        <f>AVERAGE(Q45:T45)</f>
+        <v>0.48211520714818085</v>
+      </c>
+      <c r="V45" s="12">
+        <f>U45</f>
+        <v>0.48211520714818085</v>
+      </c>
+      <c r="W45" s="12">
+        <f t="shared" ref="W45:Z45" si="66">V45</f>
+        <v>0.48211520714818085</v>
+      </c>
+      <c r="X45" s="12">
         <f t="shared" si="66"/>
-        <v>0.38647342995169082</v>
-      </c>
-      <c r="F43" s="9">
+        <v>0.48211520714818085</v>
+      </c>
+      <c r="Y45" s="12">
         <f t="shared" si="66"/>
-        <v>0.41235392320534225</v>
-      </c>
-      <c r="G43" s="9">
+        <v>0.48211520714818085</v>
+      </c>
+      <c r="Z45" s="12">
         <f t="shared" si="66"/>
-        <v>0.40957446808510639</v>
-      </c>
-      <c r="H43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.40388007054673719</v>
-      </c>
-      <c r="I43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.38445807770961143</v>
-      </c>
-      <c r="J43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.40799999999999997</v>
-      </c>
-      <c r="K43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.43487394957983194</v>
-      </c>
-      <c r="L43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.46506550218340609</v>
-      </c>
-      <c r="M43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.4461883408071749</v>
-      </c>
-      <c r="N43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.45861297539149887</v>
-      </c>
-      <c r="O43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.46532438478747201</v>
-      </c>
-      <c r="P43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.48063781321184512</v>
-      </c>
-      <c r="Q43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.47552447552447552</v>
-      </c>
-      <c r="R43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.48110831234256929</v>
-      </c>
-      <c r="S43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.48556430446194226</v>
-      </c>
-      <c r="T43" s="9">
-        <f t="shared" si="66"/>
-        <v>0.48626373626373626</v>
-      </c>
-      <c r="U43" s="9">
-        <f>AVERAGE(Q43:T43)</f>
         <v>0.48211520714818085</v>
       </c>
-      <c r="V43" s="9">
-        <f>U43</f>
-        <v>0.48211520714818085</v>
-      </c>
-      <c r="W43" s="9">
-        <f t="shared" ref="W43:Z43" si="67">V43</f>
-        <v>0.48211520714818085</v>
-      </c>
-      <c r="X43" s="9">
-        <f t="shared" si="67"/>
-        <v>0.48211520714818085</v>
-      </c>
-      <c r="Y43" s="9">
-        <f t="shared" si="67"/>
-        <v>0.48211520714818085</v>
-      </c>
-      <c r="Z43" s="9">
-        <f t="shared" si="67"/>
-        <v>0.48211520714818085</v>
-      </c>
-      <c r="AB43" s="12">
-        <f t="shared" ref="AB43:AK43" si="68">(AB9-AB15)/AB9</f>
+      <c r="AB45" s="13">
+        <f>(AB9-AB15)/AB9</f>
         <v>0.39054927302100162</v>
       </c>
-      <c r="AC43" s="12">
-        <f t="shared" si="68"/>
+      <c r="AC45" s="13">
+        <f>(AC9-AC15)/AC9</f>
         <v>0.40188679245283021</v>
       </c>
-      <c r="AD43" s="12">
-        <f t="shared" si="68"/>
+      <c r="AD45" s="13">
+        <f>(AD9-AD15)/AD9</f>
         <v>0.45101258894362345</v>
       </c>
-      <c r="AE43" s="12">
-        <f t="shared" si="68"/>
+      <c r="AE45" s="13">
+        <f>(AE9-AE15)/AE9</f>
         <v>0.47546728971962615</v>
       </c>
-      <c r="AF43" s="12">
-        <f t="shared" si="68"/>
+      <c r="AF45" s="13">
+        <f>(AF9-AF15)/AF9</f>
         <v>0.48391289694742035</v>
       </c>
-      <c r="AG43" s="12">
-        <f t="shared" si="68"/>
+      <c r="AG45" s="13">
+        <f>(AG9-AG15)/AG9</f>
         <v>0.4821152071481809</v>
       </c>
-      <c r="AH43" s="12">
-        <f t="shared" si="68"/>
+      <c r="AH45" s="13">
+        <f>(AH9-AH15)/AH9</f>
         <v>0.62639331727218661</v>
       </c>
-      <c r="AI43" s="12">
-        <f t="shared" si="68"/>
+      <c r="AI45" s="13">
+        <f>(AI9-AI15)/AI9</f>
         <v>-0.1182113672534657</v>
       </c>
-      <c r="AJ43" s="12">
-        <f t="shared" si="68"/>
+      <c r="AJ45" s="13">
+        <f>(AJ9-AJ15)/AJ9</f>
         <v>-0.64002689265679402</v>
       </c>
-      <c r="AK43" s="12">
-        <f t="shared" si="65"/>
+      <c r="AK45" s="13">
+        <f>(AK9-AK15)/AK9</f>
         <v>-0.97951327480159944</v>
       </c>
     </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
+    <row r="46" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C46" s="12">
         <f>(C11-C16)/C11</f>
         <v>-0.11688311688311688</v>
       </c>
-      <c r="D44" s="9">
-        <f t="shared" ref="D44:T44" si="69">(D11-D16)/D11</f>
+      <c r="D46" s="12">
+        <f t="shared" ref="D46:T46" si="67">(D11-D16)/D11</f>
         <v>0.11200923787528869</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E46" s="12">
+        <f t="shared" si="67"/>
+        <v>9.3106535362578333E-2</v>
+      </c>
+      <c r="F46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.12137404580152672</v>
+      </c>
+      <c r="G46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.10987573577501634</v>
+      </c>
+      <c r="H46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.18422796554009277</v>
+      </c>
+      <c r="I46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.24438742783835793</v>
+      </c>
+      <c r="J46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.21835883171070933</v>
+      </c>
+      <c r="K46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.24648318042813455</v>
+      </c>
+      <c r="L46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.24552090245520902</v>
+      </c>
+      <c r="M46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.30513468013468015</v>
+      </c>
+      <c r="N46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.25220516171185886</v>
+      </c>
+      <c r="O46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.28754578754578752</v>
+      </c>
+      <c r="P46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.30333452850484044</v>
+      </c>
+      <c r="Q46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.31420204978038069</v>
+      </c>
+      <c r="R46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.28616106333072711</v>
+      </c>
+      <c r="S46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.39534883720930231</v>
+      </c>
+      <c r="T46" s="12">
+        <f t="shared" si="67"/>
+        <v>0.20388658808537752</v>
+      </c>
+      <c r="U46" s="12">
+        <f>AVERAGE(Q46:T46)</f>
+        <v>0.29989963460144692</v>
+      </c>
+      <c r="V46" s="12">
+        <f>U46</f>
+        <v>0.29989963460144692</v>
+      </c>
+      <c r="W46" s="12">
+        <f t="shared" ref="W46:Z46" si="68">V46</f>
+        <v>0.29989963460144692</v>
+      </c>
+      <c r="X46" s="12">
+        <f t="shared" si="68"/>
+        <v>0.29989963460144692</v>
+      </c>
+      <c r="Y46" s="12">
+        <f t="shared" si="68"/>
+        <v>0.29989963460144692</v>
+      </c>
+      <c r="Z46" s="12">
+        <f t="shared" si="68"/>
+        <v>0.29989963460144692</v>
+      </c>
+      <c r="AB46" s="13">
+        <f t="shared" ref="AB46:AK46" si="69">(AB11-AB16)/AB11</f>
+        <v>7.3676132003069841E-2</v>
+      </c>
+      <c r="AC46" s="13">
         <f t="shared" si="69"/>
-        <v>9.3106535362578333E-2</v>
-      </c>
-      <c r="F44" s="9">
+        <v>0.18906379453189726</v>
+      </c>
+      <c r="AD46" s="13">
         <f t="shared" si="69"/>
-        <v>0.12137404580152672</v>
-      </c>
-      <c r="G44" s="9">
+        <v>0.26174895895300415</v>
+      </c>
+      <c r="AE46" s="13">
         <f t="shared" si="69"/>
-        <v>0.10987573577501634</v>
-      </c>
-      <c r="H44" s="9">
+        <v>0.29770573956620466</v>
+      </c>
+      <c r="AF46" s="13">
         <f t="shared" si="69"/>
-        <v>0.18422796554009277</v>
-      </c>
-      <c r="I44" s="9">
+        <v>0.29474774409144994</v>
+      </c>
+      <c r="AG46" s="13">
         <f t="shared" si="69"/>
-        <v>0.24438742783835793</v>
-      </c>
-      <c r="J44" s="9">
+        <v>0.29989963460144686</v>
+      </c>
+      <c r="AH46" s="13">
         <f t="shared" si="69"/>
-        <v>0.21835883171070933</v>
-      </c>
-      <c r="K44" s="9">
+        <v>0.47390772176475554</v>
+      </c>
+      <c r="AI46" s="13">
         <f t="shared" si="69"/>
-        <v>0.24648318042813455</v>
-      </c>
-      <c r="L44" s="9">
+        <v>0.46513255351804661</v>
+      </c>
+      <c r="AJ46" s="13">
         <f t="shared" si="69"/>
-        <v>0.24552090245520902</v>
-      </c>
-      <c r="M44" s="9">
+        <v>0.43226814436355043</v>
+      </c>
+      <c r="AK46" s="13">
         <f t="shared" si="69"/>
-        <v>0.30513468013468015</v>
-      </c>
-      <c r="N44" s="9">
-        <f t="shared" si="69"/>
-        <v>0.25220516171185886</v>
-      </c>
-      <c r="O44" s="9">
-        <f t="shared" si="69"/>
-        <v>0.28754578754578752</v>
-      </c>
-      <c r="P44" s="9">
-        <f t="shared" si="69"/>
-        <v>0.30333452850484044</v>
-      </c>
-      <c r="Q44" s="9">
-        <f t="shared" si="69"/>
-        <v>0.31420204978038069</v>
-      </c>
-      <c r="R44" s="9">
-        <f t="shared" si="69"/>
-        <v>0.28616106333072711</v>
-      </c>
-      <c r="S44" s="9">
-        <f t="shared" si="69"/>
-        <v>0.39534883720930231</v>
-      </c>
-      <c r="T44" s="9">
-        <f t="shared" si="69"/>
-        <v>0.20388658808537752</v>
-      </c>
-      <c r="U44" s="9">
-        <f>AVERAGE(Q44:T44)</f>
-        <v>0.29989963460144692</v>
-      </c>
-      <c r="V44" s="9">
-        <f>U44</f>
-        <v>0.29989963460144692</v>
-      </c>
-      <c r="W44" s="9">
-        <f t="shared" ref="W44:Z44" si="70">V44</f>
-        <v>0.29989963460144692</v>
-      </c>
-      <c r="X44" s="9">
-        <f t="shared" si="70"/>
-        <v>0.29989963460144692</v>
-      </c>
-      <c r="Y44" s="9">
-        <f t="shared" si="70"/>
-        <v>0.29989963460144692</v>
-      </c>
-      <c r="Z44" s="9">
-        <f t="shared" si="70"/>
-        <v>0.29989963460144692</v>
-      </c>
-      <c r="AB44" s="12">
-        <f t="shared" ref="AB44:AK44" si="71">(AB11-AB16)/AB11</f>
-        <v>7.3676132003069841E-2</v>
-      </c>
-      <c r="AC44" s="12">
-        <f t="shared" si="71"/>
-        <v>0.18906379453189726</v>
-      </c>
-      <c r="AD44" s="12">
-        <f t="shared" si="71"/>
-        <v>0.26174895895300415</v>
-      </c>
-      <c r="AE44" s="12">
-        <f t="shared" si="71"/>
-        <v>0.29770573956620466</v>
-      </c>
-      <c r="AF44" s="12">
-        <f t="shared" si="71"/>
-        <v>0.29474774409144994</v>
-      </c>
-      <c r="AG44" s="12">
-        <f t="shared" si="71"/>
-        <v>0.29989963460144686</v>
-      </c>
-      <c r="AH44" s="12">
-        <f t="shared" si="71"/>
-        <v>0.47390772176475554</v>
-      </c>
-      <c r="AI44" s="12">
-        <f t="shared" si="71"/>
-        <v>0.46513255351804661</v>
-      </c>
-      <c r="AJ44" s="12">
-        <f t="shared" si="71"/>
-        <v>0.43226814436355043</v>
-      </c>
-      <c r="AK44" s="12">
-        <f t="shared" si="71"/>
         <v>0.31736376733852395</v>
       </c>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
+    <row r="47" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9">
+      <c r="C47" s="12"/>
+      <c r="D47" s="12">
         <f>(D12-D17)/D12</f>
         <v>3.8199181446111868E-2</v>
       </c>
-      <c r="E45" s="9">
-        <f t="shared" ref="E45:T45" si="72">(E12-E17)/E12</f>
+      <c r="E47" s="12">
+        <f t="shared" ref="E47:T47" si="70">(E12-E17)/E12</f>
         <v>4.0121580547112463E-2</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F47" s="12">
+        <f t="shared" si="70"/>
+        <v>5.6437389770723101E-2</v>
+      </c>
+      <c r="G47" s="12">
+        <f t="shared" si="70"/>
+        <v>7.348938486663037E-2</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="70"/>
+        <v>7.7209302325581389E-2</v>
+      </c>
+      <c r="I47" s="12">
+        <f t="shared" si="70"/>
+        <v>5.9556786703601108E-2</v>
+      </c>
+      <c r="J47" s="12">
+        <f t="shared" si="70"/>
+        <v>2.7239150507848569E-2</v>
+      </c>
+      <c r="K47" s="12">
+        <f t="shared" si="70"/>
+        <v>3.5402097902097904E-2</v>
+      </c>
+      <c r="L47" s="12">
+        <f t="shared" si="70"/>
+        <v>6.4033742331288349E-2</v>
+      </c>
+      <c r="M47" s="12">
+        <f t="shared" si="70"/>
+        <v>8.8172043010752682E-2</v>
+      </c>
+      <c r="N47" s="12">
+        <f t="shared" si="70"/>
+        <v>4.1783707865168537E-2</v>
+      </c>
+      <c r="O47" s="12">
+        <f t="shared" si="70"/>
+        <v>3.828658074298711E-2</v>
+      </c>
+      <c r="P47" s="12">
+        <f t="shared" si="70"/>
+        <v>5.4497701904136574E-2</v>
+      </c>
+      <c r="Q47" s="12">
+        <f t="shared" si="70"/>
+        <v>0.10532374100719424</v>
+      </c>
+      <c r="R47" s="12">
+        <f t="shared" si="70"/>
+        <v>8.8401067932364283E-2</v>
+      </c>
+      <c r="S47" s="12">
+        <f t="shared" si="70"/>
+        <v>9.2389853137516686E-2</v>
+      </c>
+      <c r="T47" s="12">
+        <f t="shared" si="70"/>
+        <v>0.14145383104125736</v>
+      </c>
+      <c r="U47" s="12">
+        <f>AVERAGE(Q47:T47)*1.5</f>
+        <v>0.16033818491937471</v>
+      </c>
+      <c r="V47" s="12">
+        <f>AVERAGE(R47:U47)</f>
+        <v>0.12064573425762826</v>
+      </c>
+      <c r="W47" s="12">
+        <f t="shared" ref="W47:X47" si="71">AVERAGE(S47:V47)</f>
+        <v>0.12870690083894426</v>
+      </c>
+      <c r="X47" s="12">
+        <f t="shared" si="71"/>
+        <v>0.13778616276430117</v>
+      </c>
+      <c r="Y47" s="12">
+        <f>AVERAGE(U47:X47)</f>
+        <v>0.13686924569506209</v>
+      </c>
+      <c r="Z47" s="12">
+        <f>AVERAGE(V47:Y47)</f>
+        <v>0.13100201088898394</v>
+      </c>
+      <c r="AB47" s="13">
+        <f t="shared" ref="AB47:AK47" si="72">(AB12-AB17)/AB12</f>
+        <v>3.4641274010835658E-2</v>
+      </c>
+      <c r="AC47" s="13">
         <f t="shared" si="72"/>
-        <v>5.6437389770723101E-2</v>
-      </c>
-      <c r="G45" s="9">
+        <v>5.8781103498016588E-2</v>
+      </c>
+      <c r="AD47" s="13">
         <f t="shared" si="72"/>
-        <v>7.348938486663037E-2</v>
-      </c>
-      <c r="H45" s="9">
+        <v>5.8192519460793624E-2</v>
+      </c>
+      <c r="AE47" s="13">
         <f t="shared" si="72"/>
-        <v>7.7209302325581389E-2</v>
-      </c>
-      <c r="I45" s="9">
+        <v>7.4301675977653636E-2</v>
+      </c>
+      <c r="AF47" s="13">
         <f t="shared" si="72"/>
-        <v>5.9556786703601108E-2</v>
-      </c>
-      <c r="J45" s="9">
+        <v>0.12978984728554935</v>
+      </c>
+      <c r="AG47" s="13">
         <f t="shared" si="72"/>
-        <v>2.7239150507848569E-2</v>
-      </c>
-      <c r="K45" s="9">
+        <v>0.13383738549449542</v>
+      </c>
+      <c r="AH47" s="13">
         <f t="shared" si="72"/>
-        <v>3.5402097902097904E-2</v>
-      </c>
-      <c r="L45" s="9">
+        <v>0.42197422853698519</v>
+      </c>
+      <c r="AI47" s="13">
         <f t="shared" si="72"/>
-        <v>6.4033742331288349E-2</v>
-      </c>
-      <c r="M45" s="9">
+        <v>0.4430702698702837</v>
+      </c>
+      <c r="AJ47" s="13">
         <f t="shared" si="72"/>
-        <v>8.8172043010752682E-2</v>
-      </c>
-      <c r="N45" s="9">
+        <v>0.37935425403948203</v>
+      </c>
+      <c r="AK47" s="13">
         <f t="shared" si="72"/>
-        <v>4.1783707865168537E-2</v>
-      </c>
-      <c r="O45" s="9">
-        <f t="shared" si="72"/>
-        <v>3.828658074298711E-2</v>
-      </c>
-      <c r="P45" s="9">
-        <f t="shared" si="72"/>
-        <v>5.4497701904136574E-2</v>
-      </c>
-      <c r="Q45" s="9">
-        <f t="shared" si="72"/>
-        <v>0.10532374100719424</v>
-      </c>
-      <c r="R45" s="9">
-        <f t="shared" si="72"/>
-        <v>8.8401067932364283E-2</v>
-      </c>
-      <c r="S45" s="9">
-        <f t="shared" si="72"/>
-        <v>9.2389853137516686E-2</v>
-      </c>
-      <c r="T45" s="9">
-        <f t="shared" si="72"/>
-        <v>0.14145383104125736</v>
-      </c>
-      <c r="U45" s="9">
-        <f>AVERAGE(Q45:T45)*1.5</f>
-        <v>0.16033818491937471</v>
-      </c>
-      <c r="V45" s="9">
-        <f>AVERAGE(R45:U45)</f>
-        <v>0.12064573425762826</v>
-      </c>
-      <c r="W45" s="9">
-        <f t="shared" ref="W45:X45" si="73">AVERAGE(S45:V45)</f>
-        <v>0.12870690083894426</v>
-      </c>
-      <c r="X45" s="9">
-        <f t="shared" si="73"/>
-        <v>0.13778616276430117</v>
-      </c>
-      <c r="Y45" s="9">
-        <f>AVERAGE(U45:X45)</f>
-        <v>0.13686924569506209</v>
-      </c>
-      <c r="Z45" s="9">
-        <f>AVERAGE(V45:Y45)</f>
-        <v>0.13100201088898394</v>
-      </c>
-      <c r="AB45" s="12">
-        <f t="shared" ref="AB45:AK45" si="74">(AB12-AB17)/AB12</f>
-        <v>3.4641274010835658E-2</v>
-      </c>
-      <c r="AC45" s="12">
-        <f t="shared" si="74"/>
-        <v>5.8781103498016588E-2</v>
-      </c>
-      <c r="AD45" s="12">
-        <f t="shared" si="74"/>
-        <v>5.8192519460793624E-2</v>
-      </c>
-      <c r="AE45" s="12">
-        <f t="shared" si="74"/>
-        <v>7.4301675977653636E-2</v>
-      </c>
-      <c r="AF45" s="12">
-        <f t="shared" si="74"/>
-        <v>0.12978984728554935</v>
-      </c>
-      <c r="AG45" s="12">
-        <f t="shared" si="74"/>
-        <v>0.13383738549449542</v>
-      </c>
-      <c r="AH45" s="12">
-        <f t="shared" si="74"/>
-        <v>0.42197422853698519</v>
-      </c>
-      <c r="AI45" s="12">
-        <f t="shared" si="74"/>
-        <v>0.4430702698702837</v>
-      </c>
-      <c r="AJ45" s="12">
-        <f t="shared" si="74"/>
-        <v>0.37935425403948203</v>
-      </c>
-      <c r="AK45" s="12">
-        <f t="shared" si="74"/>
         <v>0.27471720722802839</v>
       </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
+    <row r="48" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C48" s="12">
         <f>C20/C13</f>
         <v>4.6118575389208785E-2</v>
       </c>
-      <c r="D46" s="9">
-        <f t="shared" ref="D46:T46" si="75">D20/D13</f>
+      <c r="D48" s="12">
+        <f t="shared" ref="D48:T48" si="73">D20/D13</f>
         <v>3.9388213062477855E-2</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E48" s="12">
+        <f t="shared" si="73"/>
+        <v>3.4166122867530534E-2</v>
+      </c>
+      <c r="F48" s="12">
+        <f t="shared" si="73"/>
+        <v>3.3308660251665435E-2</v>
+      </c>
+      <c r="G48" s="12">
+        <f t="shared" si="73"/>
+        <v>3.3048994813322477E-2</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="73"/>
+        <v>3.7830464957676418E-2</v>
+      </c>
+      <c r="I48" s="12">
+        <f t="shared" si="73"/>
+        <v>4.9721627408993579E-2</v>
+      </c>
+      <c r="J48" s="12">
+        <f t="shared" si="73"/>
+        <v>4.3469622918901739E-2</v>
+      </c>
+      <c r="K48" s="12">
+        <f t="shared" si="73"/>
+        <v>5.4035021829961033E-2</v>
+      </c>
+      <c r="L48" s="12">
+        <f t="shared" si="73"/>
+        <v>4.211764705882353E-2</v>
+      </c>
+      <c r="M48" s="12">
+        <f t="shared" si="73"/>
+        <v>4.1259629894368995E-2</v>
+      </c>
+      <c r="N48" s="12">
+        <f t="shared" si="73"/>
+        <v>4.9636285836542574E-2</v>
+      </c>
+      <c r="O48" s="12">
+        <f t="shared" si="73"/>
+        <v>7.2873028187225242E-2</v>
+      </c>
+      <c r="P48" s="12">
+        <f t="shared" si="73"/>
+        <v>7.0634779516358465E-2</v>
+      </c>
+      <c r="Q48" s="12">
+        <f t="shared" si="73"/>
+        <v>5.8017440825769713E-2</v>
+      </c>
+      <c r="R48" s="12">
+        <f t="shared" si="73"/>
+        <v>7.1603550058230589E-2</v>
+      </c>
+      <c r="S48" s="12">
+        <f t="shared" si="73"/>
+        <v>8.6925447804529418E-2</v>
+      </c>
+      <c r="T48" s="12">
+        <f t="shared" si="73"/>
+        <v>8.3970817396231759E-2</v>
+      </c>
+      <c r="U48" s="12">
+        <f>AVERAGE(Q48:T48)</f>
+        <v>7.5129314021190371E-2</v>
+      </c>
+      <c r="V48" s="12">
+        <f>U48</f>
+        <v>7.5129314021190371E-2</v>
+      </c>
+      <c r="W48" s="12">
+        <f t="shared" ref="W48:Z49" si="74">V48</f>
+        <v>7.5129314021190371E-2</v>
+      </c>
+      <c r="X48" s="12">
+        <f t="shared" si="74"/>
+        <v>7.5129314021190371E-2</v>
+      </c>
+      <c r="Y48" s="12">
+        <f t="shared" si="74"/>
+        <v>7.5129314021190371E-2</v>
+      </c>
+      <c r="Z48" s="12">
+        <f t="shared" si="74"/>
+        <v>7.5129314021190371E-2</v>
+      </c>
+      <c r="AB48" s="13">
+        <f t="shared" ref="AB48:AK48" si="75">AB20/AB13</f>
+        <v>3.7747661486337188E-2</v>
+      </c>
+      <c r="AC48" s="13">
         <f t="shared" si="75"/>
-        <v>3.4166122867530534E-2</v>
-      </c>
-      <c r="F46" s="9">
+        <v>4.1013505833238609E-2</v>
+      </c>
+      <c r="AD48" s="13">
         <f t="shared" si="75"/>
-        <v>3.3308660251665435E-2</v>
-      </c>
-      <c r="G46" s="9">
+        <v>4.6473538745009722E-2</v>
+      </c>
+      <c r="AE48" s="13">
         <f t="shared" si="75"/>
-        <v>3.3048994813322477E-2</v>
-      </c>
-      <c r="H46" s="9">
+        <v>6.7607327027112529E-2</v>
+      </c>
+      <c r="AF48" s="13">
         <f t="shared" si="75"/>
-        <v>3.7830464957676418E-2</v>
-      </c>
-      <c r="I46" s="9">
+        <v>7.9998079244639503E-2</v>
+      </c>
+      <c r="AG48" s="13">
         <f t="shared" si="75"/>
-        <v>4.9721627408993579E-2</v>
-      </c>
-      <c r="J46" s="9">
+        <v>7.5129314021190371E-2</v>
+      </c>
+      <c r="AH48" s="13">
         <f t="shared" si="75"/>
-        <v>4.3469622918901739E-2</v>
-      </c>
-      <c r="K46" s="9">
+        <v>7.5129314021190371E-2</v>
+      </c>
+      <c r="AI48" s="13">
         <f t="shared" si="75"/>
-        <v>5.4035021829961033E-2</v>
-      </c>
-      <c r="L46" s="9">
+        <v>5.3187750211223878E-2</v>
+      </c>
+      <c r="AJ48" s="13">
         <f t="shared" si="75"/>
-        <v>4.211764705882353E-2</v>
-      </c>
-      <c r="M46" s="9">
+        <v>4.4213189082406588E-2</v>
+      </c>
+      <c r="AK48" s="13">
         <f t="shared" si="75"/>
-        <v>4.1259629894368995E-2</v>
-      </c>
-      <c r="N46" s="9">
-        <f t="shared" si="75"/>
-        <v>4.9636285836542574E-2</v>
-      </c>
-      <c r="O46" s="9">
-        <f t="shared" si="75"/>
-        <v>7.2873028187225242E-2</v>
-      </c>
-      <c r="P46" s="9">
-        <f t="shared" si="75"/>
-        <v>7.0634779516358465E-2</v>
-      </c>
-      <c r="Q46" s="9">
-        <f t="shared" si="75"/>
-        <v>5.8017440825769713E-2</v>
-      </c>
-      <c r="R46" s="9">
-        <f t="shared" si="75"/>
-        <v>7.1603550058230589E-2</v>
-      </c>
-      <c r="S46" s="9">
-        <f t="shared" si="75"/>
-        <v>8.6925447804529418E-2</v>
-      </c>
-      <c r="T46" s="9">
-        <f t="shared" si="75"/>
-        <v>8.3970817396231759E-2</v>
-      </c>
-      <c r="U46" s="9">
-        <f>AVERAGE(Q46:T46)</f>
-        <v>7.5129314021190371E-2</v>
-      </c>
-      <c r="V46" s="9">
-        <f>U46</f>
-        <v>7.5129314021190371E-2</v>
-      </c>
-      <c r="W46" s="9">
-        <f t="shared" ref="W46:Z47" si="76">V46</f>
-        <v>7.5129314021190371E-2</v>
-      </c>
-      <c r="X46" s="9">
-        <f t="shared" si="76"/>
-        <v>7.5129314021190371E-2</v>
-      </c>
-      <c r="Y46" s="9">
-        <f t="shared" si="76"/>
-        <v>7.5129314021190371E-2</v>
-      </c>
-      <c r="Z46" s="9">
-        <f t="shared" si="76"/>
-        <v>7.5129314021190371E-2</v>
-      </c>
-      <c r="AB46" s="12">
-        <f t="shared" ref="AB46:AK46" si="77">AB20/AB13</f>
-        <v>3.7747661486337188E-2</v>
-      </c>
-      <c r="AC46" s="12">
-        <f t="shared" si="77"/>
-        <v>4.1013505833238609E-2</v>
-      </c>
-      <c r="AD46" s="12">
-        <f t="shared" si="77"/>
-        <v>4.6473538745009722E-2</v>
-      </c>
-      <c r="AE46" s="12">
-        <f t="shared" si="77"/>
-        <v>6.7607327027112529E-2</v>
-      </c>
-      <c r="AF46" s="12">
-        <f t="shared" si="77"/>
-        <v>7.9998079244639503E-2</v>
-      </c>
-      <c r="AG46" s="12">
-        <f t="shared" si="77"/>
-        <v>7.5129314021190371E-2</v>
-      </c>
-      <c r="AH46" s="12">
-        <f t="shared" si="77"/>
-        <v>7.5129314021190371E-2</v>
-      </c>
-      <c r="AI46" s="12">
-        <f t="shared" si="77"/>
-        <v>5.3187750211223878E-2</v>
-      </c>
-      <c r="AJ46" s="12">
-        <f t="shared" si="77"/>
-        <v>4.4213189082406588E-2</v>
-      </c>
-      <c r="AK46" s="12">
-        <f t="shared" si="77"/>
         <v>4.1982422759807916E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
+    <row r="49" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C49" s="12">
         <f>C21/C13</f>
         <v>5.2889741949242911E-2</v>
       </c>
-      <c r="D47" s="9">
-        <f t="shared" ref="D47:T47" si="78">D21/D13</f>
+      <c r="D49" s="12">
+        <f t="shared" ref="D49:T49" si="76">D21/D13</f>
         <v>5.6749734262430615E-2</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E49" s="12">
+        <f t="shared" si="76"/>
+        <v>4.4793511699449985E-2</v>
+      </c>
+      <c r="F49" s="12">
+        <f t="shared" si="76"/>
+        <v>4.2437700468788551E-2</v>
+      </c>
+      <c r="G49" s="12">
+        <f t="shared" si="76"/>
+        <v>4.6122851386686099E-2</v>
+      </c>
+      <c r="H49" s="12">
+        <f t="shared" si="76"/>
+        <v>4.7779516187266821E-2</v>
+      </c>
+      <c r="I49" s="12">
+        <f t="shared" si="76"/>
+        <v>5.3661670235546036E-2</v>
+      </c>
+      <c r="J49" s="12">
+        <f t="shared" si="76"/>
+        <v>5.0860253506576074E-2</v>
+      </c>
+      <c r="K49" s="12">
+        <f t="shared" si="76"/>
+        <v>6.4504013896061224E-2</v>
+      </c>
+      <c r="L49" s="12">
+        <f t="shared" si="76"/>
+        <v>5.0078431372549019E-2</v>
+      </c>
+      <c r="M49" s="12">
+        <f t="shared" si="76"/>
+        <v>4.7097132872686839E-2</v>
+      </c>
+      <c r="N49" s="12">
+        <f t="shared" si="76"/>
+        <v>5.1075582526160193E-2</v>
+      </c>
+      <c r="O49" s="12">
+        <f t="shared" si="76"/>
+        <v>6.470131885182312E-2</v>
+      </c>
+      <c r="P49" s="12">
+        <f t="shared" si="76"/>
+        <v>6.0721906116642958E-2</v>
+      </c>
+      <c r="Q49" s="12">
+        <f t="shared" si="76"/>
+        <v>5.5597081331197722E-2</v>
+      </c>
+      <c r="R49" s="12">
+        <f t="shared" si="76"/>
+        <v>6.6463194249226934E-2</v>
+      </c>
+      <c r="S49" s="12">
+        <f t="shared" si="76"/>
+        <v>8.1877875552776161E-2</v>
+      </c>
+      <c r="T49" s="12">
+        <f t="shared" si="76"/>
+        <v>7.0194078481371297E-2</v>
+      </c>
+      <c r="U49" s="12">
+        <f>AVERAGE(Q49:T49)</f>
+        <v>6.8533057403643016E-2</v>
+      </c>
+      <c r="V49" s="12">
+        <f>U49</f>
+        <v>6.8533057403643016E-2</v>
+      </c>
+      <c r="W49" s="12">
+        <f t="shared" si="74"/>
+        <v>6.8533057403643016E-2</v>
+      </c>
+      <c r="X49" s="12">
+        <f t="shared" si="74"/>
+        <v>6.8533057403643016E-2</v>
+      </c>
+      <c r="Y49" s="12">
+        <f t="shared" si="74"/>
+        <v>6.8533057403643016E-2</v>
+      </c>
+      <c r="Z49" s="12">
+        <f t="shared" si="74"/>
+        <v>6.8533057403643016E-2</v>
+      </c>
+      <c r="AB49" s="13">
+        <f t="shared" ref="AB49:AK49" si="77">AB21/AB13</f>
+        <v>4.8439763325231394E-2</v>
+      </c>
+      <c r="AC49" s="13">
+        <f t="shared" si="77"/>
+        <v>4.9600611740878139E-2</v>
+      </c>
+      <c r="AD49" s="13">
+        <f t="shared" si="77"/>
+        <v>5.2717780734977994E-2</v>
+      </c>
+      <c r="AE49" s="13">
+        <f t="shared" si="77"/>
+        <v>6.1522562139475045E-2</v>
+      </c>
+      <c r="AF49" s="13">
+        <f t="shared" si="77"/>
+        <v>7.1808898562598117E-2</v>
+      </c>
+      <c r="AG49" s="13">
+        <f t="shared" si="77"/>
+        <v>6.8533057403643016E-2</v>
+      </c>
+      <c r="AH49" s="13">
+        <f t="shared" si="77"/>
+        <v>6.8533057403643016E-2</v>
+      </c>
+      <c r="AI49" s="13">
+        <f t="shared" si="77"/>
+        <v>5.6739081902885444E-2</v>
+      </c>
+      <c r="AJ49" s="13">
+        <f t="shared" si="77"/>
+        <v>5.1634801016039809E-2</v>
+      </c>
+      <c r="AK49" s="13">
+        <f t="shared" si="77"/>
+        <v>5.0361511280239198E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="12">
+        <v>0</v>
+      </c>
+      <c r="D50" s="12">
+        <v>0</v>
+      </c>
+      <c r="E50" s="12">
+        <v>0</v>
+      </c>
+      <c r="F50" s="12">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12">
+        <v>0</v>
+      </c>
+      <c r="H50" s="12">
+        <v>0</v>
+      </c>
+      <c r="I50" s="12">
+        <v>0</v>
+      </c>
+      <c r="J50" s="12">
+        <v>0</v>
+      </c>
+      <c r="K50" s="12">
+        <v>0</v>
+      </c>
+      <c r="L50" s="12">
+        <v>0</v>
+      </c>
+      <c r="M50" s="12">
+        <v>0</v>
+      </c>
+      <c r="N50" s="12">
+        <v>0</v>
+      </c>
+      <c r="O50" s="12">
+        <v>0</v>
+      </c>
+      <c r="P50" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="12">
+        <v>0</v>
+      </c>
+      <c r="R50" s="12">
+        <v>0</v>
+      </c>
+      <c r="S50" s="12">
+        <v>0</v>
+      </c>
+      <c r="T50" s="12">
+        <v>0</v>
+      </c>
+      <c r="U50" s="12">
+        <v>0</v>
+      </c>
+      <c r="V50" s="12">
+        <v>0</v>
+      </c>
+      <c r="W50" s="12">
+        <v>0</v>
+      </c>
+      <c r="X50" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="13">
+        <f t="shared" ref="AB50:AK50" si="78">AB22/AB13</f>
+        <v>2.160516559868405E-3</v>
+      </c>
+      <c r="AC50" s="13">
         <f t="shared" si="78"/>
-        <v>4.4793511699449985E-2</v>
-      </c>
-      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="13">
         <f t="shared" si="78"/>
-        <v>4.2437700468788551E-2</v>
-      </c>
-      <c r="G47" s="9">
+        <v>7.0017401985873681E-3</v>
+      </c>
+      <c r="AE50" s="13">
         <f t="shared" si="78"/>
-        <v>4.6122851386686099E-2</v>
-      </c>
-      <c r="H47" s="9">
+        <v>5.2094867495544516E-3</v>
+      </c>
+      <c r="AF50" s="13">
         <f t="shared" si="78"/>
-        <v>4.7779516187266821E-2</v>
-      </c>
-      <c r="I47" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="13">
         <f t="shared" si="78"/>
-        <v>5.3661670235546036E-2</v>
-      </c>
-      <c r="J47" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="13">
         <f t="shared" si="78"/>
-        <v>5.0860253506576074E-2</v>
-      </c>
-      <c r="K47" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="13">
         <f t="shared" si="78"/>
-        <v>6.4504013896061224E-2</v>
-      </c>
-      <c r="L47" s="9">
+        <v>1.2681384782720143E-3</v>
+      </c>
+      <c r="AJ50" s="13">
         <f t="shared" si="78"/>
-        <v>5.0078431372549019E-2</v>
-      </c>
-      <c r="M47" s="9">
+        <v>8.5733702449397261E-4</v>
+      </c>
+      <c r="AK50" s="13">
         <f t="shared" si="78"/>
-        <v>4.7097132872686839E-2</v>
-      </c>
-      <c r="N47" s="9">
-        <f t="shared" si="78"/>
-        <v>5.1075582526160193E-2</v>
-      </c>
-      <c r="O47" s="9">
-        <f t="shared" si="78"/>
-        <v>6.470131885182312E-2</v>
-      </c>
-      <c r="P47" s="9">
-        <f t="shared" si="78"/>
-        <v>6.0721906116642958E-2</v>
-      </c>
-      <c r="Q47" s="9">
-        <f t="shared" si="78"/>
-        <v>5.5597081331197722E-2</v>
-      </c>
-      <c r="R47" s="9">
-        <f t="shared" si="78"/>
-        <v>6.6463194249226934E-2</v>
-      </c>
-      <c r="S47" s="9">
-        <f t="shared" si="78"/>
-        <v>8.1877875552776161E-2</v>
-      </c>
-      <c r="T47" s="9">
-        <f t="shared" si="78"/>
-        <v>7.0194078481371297E-2</v>
-      </c>
-      <c r="U47" s="9">
-        <f>AVERAGE(Q47:T47)</f>
-        <v>6.8533057403643016E-2</v>
-      </c>
-      <c r="V47" s="9">
-        <f>U47</f>
-        <v>6.8533057403643016E-2</v>
-      </c>
-      <c r="W47" s="9">
-        <f t="shared" si="76"/>
-        <v>6.8533057403643016E-2</v>
-      </c>
-      <c r="X47" s="9">
-        <f t="shared" si="76"/>
-        <v>6.8533057403643016E-2</v>
-      </c>
-      <c r="Y47" s="9">
-        <f t="shared" si="76"/>
-        <v>6.8533057403643016E-2</v>
-      </c>
-      <c r="Z47" s="9">
-        <f t="shared" si="76"/>
-        <v>6.8533057403643016E-2</v>
-      </c>
-      <c r="AB47" s="12">
-        <f t="shared" ref="AB47:AK47" si="79">AB21/AB13</f>
-        <v>4.8439763325231394E-2</v>
-      </c>
-      <c r="AC47" s="12">
-        <f t="shared" si="79"/>
-        <v>4.9600611740878139E-2</v>
-      </c>
-      <c r="AD47" s="12">
-        <f t="shared" si="79"/>
-        <v>5.2717780734977994E-2</v>
-      </c>
-      <c r="AE47" s="12">
-        <f t="shared" si="79"/>
-        <v>6.1522562139475045E-2</v>
-      </c>
-      <c r="AF47" s="12">
-        <f t="shared" si="79"/>
-        <v>7.1808898562598117E-2</v>
-      </c>
-      <c r="AG47" s="12">
-        <f t="shared" si="79"/>
-        <v>6.8533057403643016E-2</v>
-      </c>
-      <c r="AH47" s="12">
-        <f t="shared" si="79"/>
-        <v>6.8533057403643016E-2</v>
-      </c>
-      <c r="AI47" s="12">
-        <f t="shared" si="79"/>
-        <v>5.6739081902885444E-2</v>
-      </c>
-      <c r="AJ47" s="12">
-        <f t="shared" si="79"/>
-        <v>5.1634801016039809E-2</v>
-      </c>
-      <c r="AK47" s="12">
-        <f t="shared" si="79"/>
-        <v>5.0361511280239198E-2</v>
+        <v>3.1167889825133642E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" s="9">
-        <v>0</v>
-      </c>
-      <c r="D48" s="9">
-        <v>0</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0</v>
-      </c>
-      <c r="F48" s="9">
-        <v>0</v>
-      </c>
-      <c r="G48" s="9">
-        <v>0</v>
-      </c>
-      <c r="H48" s="9">
-        <v>0</v>
-      </c>
-      <c r="I48" s="9">
-        <v>0</v>
-      </c>
-      <c r="J48" s="9">
-        <v>0</v>
-      </c>
-      <c r="K48" s="9">
-        <v>0</v>
-      </c>
-      <c r="L48" s="9">
-        <v>0</v>
-      </c>
-      <c r="M48" s="9">
-        <v>0</v>
-      </c>
-      <c r="N48" s="9">
-        <v>0</v>
-      </c>
-      <c r="O48" s="9">
-        <v>0</v>
-      </c>
-      <c r="P48" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="9">
-        <v>0</v>
-      </c>
-      <c r="R48" s="9">
-        <v>0</v>
-      </c>
-      <c r="S48" s="9">
-        <v>0</v>
-      </c>
-      <c r="T48" s="9">
-        <v>0</v>
-      </c>
-      <c r="U48" s="9">
-        <v>0</v>
-      </c>
-      <c r="V48" s="9">
-        <v>0</v>
-      </c>
-      <c r="W48" s="9">
-        <v>0</v>
-      </c>
-      <c r="X48" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="12">
-        <f t="shared" ref="AB48:AK48" si="80">AB22/AB13</f>
-        <v>2.160516559868405E-3</v>
-      </c>
-      <c r="AC48" s="12">
-        <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="AD48" s="12">
-        <f t="shared" si="80"/>
-        <v>7.0017401985873681E-3</v>
-      </c>
-      <c r="AE48" s="12">
-        <f t="shared" si="80"/>
-        <v>5.2094867495544516E-3</v>
-      </c>
-      <c r="AF48" s="12">
-        <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="AG48" s="12">
-        <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="AH48" s="12">
-        <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="AI48" s="12">
-        <f t="shared" si="80"/>
-        <v>1.2681384782720143E-3</v>
-      </c>
-      <c r="AJ48" s="12">
-        <f t="shared" si="80"/>
-        <v>8.5733702449397261E-4</v>
-      </c>
-      <c r="AK48" s="12">
-        <f t="shared" si="80"/>
-        <v>3.1167889825133642E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
+    <row r="51" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C51" s="12">
         <f>C29/C28</f>
         <v>9.5421952564809703E-2</v>
       </c>
-      <c r="D49" s="9">
-        <f t="shared" ref="D49:T49" si="81">D29/D28</f>
+      <c r="D51" s="12">
+        <f t="shared" ref="D51:T51" si="79">D29/D28</f>
         <v>8.286176232821342E-2</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E51" s="12">
+        <f t="shared" si="79"/>
+        <v>8.3883388338833881E-2</v>
+      </c>
+      <c r="F51" s="12">
+        <f t="shared" si="79"/>
+        <v>6.929450163193572E-2</v>
+      </c>
+      <c r="G51" s="12">
+        <f t="shared" si="79"/>
+        <v>9.3214285714285708E-2</v>
+      </c>
+      <c r="H51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.10997616615594144</v>
+      </c>
+      <c r="I51" s="12">
+        <f t="shared" si="79"/>
+        <v>8.1662591687041569E-2</v>
+      </c>
+      <c r="J51" s="12">
+        <f t="shared" si="79"/>
+        <v>-2.6252852578731174</v>
+      </c>
+      <c r="K51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.26336123631680619</v>
+      </c>
+      <c r="L51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.20826709062003179</v>
+      </c>
+      <c r="M51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.21569329989251165</v>
+      </c>
+      <c r="N51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.15694092062341428</v>
+      </c>
+      <c r="O51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.28692699490662138</v>
+      </c>
+      <c r="P51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.23176242737249839</v>
+      </c>
+      <c r="Q51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.29096477794793263</v>
+      </c>
+      <c r="R51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.275190516511431</v>
+      </c>
+      <c r="S51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.34358288770053474</v>
+      </c>
+      <c r="T51" s="12">
+        <f t="shared" si="79"/>
+        <v>0.15124153498871332</v>
+      </c>
+      <c r="U51" s="12">
+        <f>AVERAGE(Q51:T51)</f>
+        <v>0.26524492928715293</v>
+      </c>
+      <c r="V51" s="12">
+        <f>U51</f>
+        <v>0.26524492928715293</v>
+      </c>
+      <c r="W51" s="12">
+        <f t="shared" ref="W51:Z51" si="80">V51</f>
+        <v>0.26524492928715293</v>
+      </c>
+      <c r="X51" s="12">
+        <f t="shared" si="80"/>
+        <v>0.26524492928715293</v>
+      </c>
+      <c r="Y51" s="12">
+        <f t="shared" si="80"/>
+        <v>0.26524492928715293</v>
+      </c>
+      <c r="Z51" s="12">
+        <f t="shared" si="80"/>
+        <v>0.26524492928715293</v>
+      </c>
+      <c r="AB51" s="13">
+        <f t="shared" ref="AB51:AK51" si="81">AB29/AB28</f>
+        <v>8.2513302718857054E-2</v>
+      </c>
+      <c r="AC51" s="13">
         <f t="shared" si="81"/>
-        <v>8.3883388338833881E-2</v>
-      </c>
-      <c r="F49" s="9">
+        <v>-0.50145392559911761</v>
+      </c>
+      <c r="AD51" s="13">
         <f t="shared" si="81"/>
-        <v>6.929450163193572E-2</v>
-      </c>
-      <c r="G49" s="9">
+        <v>0.20433815350389323</v>
+      </c>
+      <c r="AE51" s="13">
         <f t="shared" si="81"/>
-        <v>9.3214285714285708E-2</v>
-      </c>
-      <c r="H49" s="9">
+        <v>0.26960970064418338</v>
+      </c>
+      <c r="AF51" s="13">
         <f t="shared" si="81"/>
-        <v>0.10997616615594144</v>
-      </c>
-      <c r="I49" s="9">
+        <v>0.24915500924608056</v>
+      </c>
+      <c r="AG51" s="13">
         <f t="shared" si="81"/>
-        <v>8.1662591687041569E-2</v>
-      </c>
-      <c r="J49" s="9">
+        <v>0.26524492928715293</v>
+      </c>
+      <c r="AH51" s="13">
         <f t="shared" si="81"/>
-        <v>-2.6252852578731174</v>
-      </c>
-      <c r="K49" s="9">
+        <v>0.26524492928715293</v>
+      </c>
+      <c r="AI51" s="13">
         <f t="shared" si="81"/>
-        <v>0.26336123631680619</v>
-      </c>
-      <c r="L49" s="9">
+        <v>0.12237770363035248</v>
+      </c>
+      <c r="AJ51" s="13">
         <f t="shared" si="81"/>
-        <v>0.20826709062003179</v>
-      </c>
-      <c r="M49" s="9">
+        <v>-0.13147350471898026</v>
+      </c>
+      <c r="AK51" s="13">
         <f t="shared" si="81"/>
-        <v>0.21569329989251165</v>
-      </c>
-      <c r="N49" s="9">
-        <f t="shared" si="81"/>
-        <v>0.15694092062341428</v>
-      </c>
-      <c r="O49" s="9">
-        <f t="shared" si="81"/>
-        <v>0.28692699490662138</v>
-      </c>
-      <c r="P49" s="9">
-        <f t="shared" si="81"/>
-        <v>0.23176242737249839</v>
-      </c>
-      <c r="Q49" s="9">
-        <f t="shared" si="81"/>
-        <v>0.29096477794793263</v>
-      </c>
-      <c r="R49" s="9">
-        <f t="shared" si="81"/>
-        <v>0.275190516511431</v>
-      </c>
-      <c r="S49" s="9">
-        <f t="shared" si="81"/>
-        <v>0.34358288770053474</v>
-      </c>
-      <c r="T49" s="9">
-        <f t="shared" si="81"/>
-        <v>0.15124153498871332</v>
-      </c>
-      <c r="U49" s="9">
-        <f>AVERAGE(Q49:T49)</f>
-        <v>0.26524492928715293</v>
-      </c>
-      <c r="V49" s="9">
-        <f>U49</f>
-        <v>0.26524492928715293</v>
-      </c>
-      <c r="W49" s="9">
-        <f t="shared" ref="W49:Z49" si="82">V49</f>
-        <v>0.26524492928715293</v>
-      </c>
-      <c r="X49" s="9">
+        <v>-6.21748974970932E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G53" s="14">
+        <f t="shared" ref="G53:T53" si="82">(G8+G9+G10)/(C8+C9+C10)-1</f>
+        <v>0.18397485321155327</v>
+      </c>
+      <c r="H53" s="14">
         <f t="shared" si="82"/>
-        <v>0.26524492928715293</v>
-      </c>
-      <c r="Y49" s="9">
+        <v>0.4565128064648678</v>
+      </c>
+      <c r="I53" s="14">
         <f t="shared" si="82"/>
-        <v>0.26524492928715293</v>
-      </c>
-      <c r="Z49" s="9">
+        <v>4.9914401883158543E-2</v>
+      </c>
+      <c r="J53" s="14">
         <f t="shared" si="82"/>
-        <v>0.26524492928715293</v>
-      </c>
-      <c r="AB49" s="12">
-        <f t="shared" ref="AB49:AK49" si="83">AB29/AB28</f>
-        <v>8.2513302718857054E-2</v>
-      </c>
-      <c r="AC49" s="12">
+        <v>1.2014830806777121E-2</v>
+      </c>
+      <c r="K53" s="14">
+        <f t="shared" si="82"/>
+        <v>-0.12948955567800435</v>
+      </c>
+      <c r="L53" s="14">
+        <f t="shared" si="82"/>
+        <v>-6.5356403987210876E-2</v>
+      </c>
+      <c r="M53" s="14">
+        <f t="shared" si="82"/>
+        <v>1.9923566878981003E-2</v>
+      </c>
+      <c r="N53" s="14">
+        <f t="shared" si="82"/>
+        <v>-8.1853174419143859E-2</v>
+      </c>
+      <c r="O53" s="14">
+        <f t="shared" si="82"/>
+        <v>-0.19628265623201746</v>
+      </c>
+      <c r="P53" s="14">
+        <f t="shared" si="82"/>
+        <v>-0.16183720696247106</v>
+      </c>
+      <c r="Q53" s="14">
+        <f t="shared" si="82"/>
+        <v>5.9402478017585914E-2</v>
+      </c>
+      <c r="R53" s="14">
+        <f t="shared" si="82"/>
+        <v>-0.10632387109809072</v>
+      </c>
+      <c r="S53" s="14">
+        <f t="shared" si="82"/>
+        <v>0.16231116202477258</v>
+      </c>
+      <c r="T53" s="14">
+        <f t="shared" si="82"/>
+        <v>0.23137866874737401</v>
+      </c>
+      <c r="AB53" s="13"/>
+      <c r="AC53" s="13">
+        <f t="shared" ref="AC53:AK53" si="83">(AC8+AC9+AC10)/(AB8+AB9+AB10)-1</f>
+        <v>0.15332624331812705</v>
+      </c>
+      <c r="AD53" s="13">
         <f t="shared" si="83"/>
-        <v>-0.50145392559911761</v>
-      </c>
-      <c r="AD49" s="12">
+        <v>-6.4900083718560042E-2</v>
+      </c>
+      <c r="AE53" s="13">
         <f t="shared" si="83"/>
-        <v>0.20433815350389323</v>
-      </c>
-      <c r="AE49" s="12">
+        <v>-9.7885039574412858E-2</v>
+      </c>
+      <c r="AF53" s="13">
         <f t="shared" si="83"/>
-        <v>0.26960970064418338</v>
-      </c>
-      <c r="AF49" s="12">
+        <v>8.4910680896355339E-2</v>
+      </c>
+      <c r="AG53" s="13">
         <f t="shared" si="83"/>
-        <v>0.24915500924608056</v>
-      </c>
-      <c r="AG49" s="12">
+        <v>2.8967446423482368E-3</v>
+      </c>
+      <c r="AH53" s="13">
         <f t="shared" si="83"/>
-        <v>0.26524492928715293</v>
-      </c>
-      <c r="AH49" s="12">
+        <v>4.9015836505922339E-2</v>
+      </c>
+      <c r="AI53" s="13">
         <f t="shared" si="83"/>
-        <v>0.26524492928715293</v>
-      </c>
-      <c r="AI49" s="12">
+        <v>4.9061822081394091E-2</v>
+      </c>
+      <c r="AJ53" s="13">
         <f t="shared" si="83"/>
-        <v>0.12237770363035248</v>
-      </c>
-      <c r="AJ49" s="12">
+        <v>4.9105698159194855E-2</v>
+      </c>
+      <c r="AK53" s="13">
         <f t="shared" si="83"/>
-        <v>-0.13147350471898026</v>
-      </c>
-      <c r="AK49" s="12">
-        <f t="shared" si="83"/>
-        <v>-6.21748974970932E-2</v>
+        <v>4.9147557922548213E-2</v>
       </c>
     </row>
-    <row r="51" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G51" s="5">
-        <f t="shared" ref="G51:T51" si="84">(G8+G9+G10)/(C8+C9+C10)-1</f>
-        <v>0.18397485321155327</v>
-      </c>
-      <c r="H51" s="5">
+    <row r="54" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" s="14">
+        <f t="shared" ref="G54:S54" si="84">G12/C12-1</f>
+        <v>0.43627834245504293</v>
+      </c>
+      <c r="H54" s="14">
         <f t="shared" si="84"/>
-        <v>0.4565128064648678</v>
-      </c>
-      <c r="I51" s="5">
+        <v>0.46657571623465222</v>
+      </c>
+      <c r="I54" s="14">
         <f t="shared" si="84"/>
-        <v>4.9914401883158543E-2</v>
-      </c>
-      <c r="J51" s="5">
+        <v>0.31671732522796359</v>
+      </c>
+      <c r="J54" s="14">
         <f t="shared" si="84"/>
-        <v>1.2014830806777121E-2</v>
-      </c>
-      <c r="K51" s="5">
+        <v>0.27336860670194008</v>
+      </c>
+      <c r="K54" s="14">
         <f t="shared" si="84"/>
-        <v>-0.12948955567800435</v>
-      </c>
-      <c r="L51" s="5">
+        <v>0.24550898203592819</v>
+      </c>
+      <c r="L54" s="14">
         <f t="shared" si="84"/>
-        <v>-6.5356403987210876E-2</v>
-      </c>
-      <c r="M51" s="5">
+        <v>0.21302325581395354</v>
+      </c>
+      <c r="M54" s="14">
         <f t="shared" si="84"/>
-        <v>1.9923566878981003E-2</v>
-      </c>
-      <c r="N51" s="5">
+        <v>0.28808864265927969</v>
+      </c>
+      <c r="N54" s="14">
         <f t="shared" si="84"/>
-        <v>-8.1853174419143859E-2</v>
-      </c>
-      <c r="O51" s="5">
+        <v>0.31486611265004627</v>
+      </c>
+      <c r="O54" s="14">
         <f t="shared" si="84"/>
-        <v>-0.19628265623201746</v>
-      </c>
-      <c r="P51" s="5">
+        <v>0.15297202797202791</v>
+      </c>
+      <c r="P54" s="14">
         <f t="shared" si="84"/>
-        <v>-0.16183720696247106</v>
-      </c>
-      <c r="Q51" s="5">
+        <v>0.16794478527607359</v>
+      </c>
+      <c r="Q54" s="14">
         <f t="shared" si="84"/>
-        <v>5.9402478017585914E-2</v>
-      </c>
-      <c r="R51" s="5">
+        <v>0.24551971326164868</v>
+      </c>
+      <c r="R54" s="14">
         <f t="shared" si="84"/>
-        <v>-0.10632387109809072</v>
-      </c>
-      <c r="S51" s="5">
+        <v>0.1836376404494382</v>
+      </c>
+      <c r="S54" s="14">
         <f t="shared" si="84"/>
-        <v>0.16231116202477258</v>
-      </c>
-      <c r="T51" s="5">
-        <f t="shared" si="84"/>
-        <v>0.23137866874737401</v>
-      </c>
-      <c r="AB51" s="12"/>
-      <c r="AC51" s="12">
-        <f t="shared" ref="AC51:AK51" si="85">(AC8+AC9+AC10)/(AB8+AB9+AB10)-1</f>
-        <v>0.15332624331812705</v>
-      </c>
-      <c r="AD51" s="12">
-        <f t="shared" si="85"/>
-        <v>-6.4900083718560042E-2</v>
-      </c>
-      <c r="AE51" s="12">
-        <f t="shared" si="85"/>
-        <v>-9.7885039574412858E-2</v>
-      </c>
-      <c r="AF51" s="12">
-        <f t="shared" si="85"/>
-        <v>8.4910680896355339E-2</v>
-      </c>
-      <c r="AG51" s="12">
-        <f t="shared" si="85"/>
-        <v>2.8967446423482368E-3</v>
-      </c>
-      <c r="AH51" s="12">
-        <f t="shared" si="85"/>
-        <v>4.9015836505922339E-2</v>
-      </c>
-      <c r="AI51" s="12">
-        <f t="shared" si="85"/>
-        <v>4.9061822081394091E-2</v>
-      </c>
-      <c r="AJ51" s="12">
-        <f t="shared" si="85"/>
-        <v>4.9105698159194855E-2</v>
-      </c>
-      <c r="AK51" s="12">
-        <f t="shared" si="85"/>
-        <v>4.9147557922548213E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G52" s="5">
-        <f t="shared" ref="G52:S52" si="86">G12/C12-1</f>
-        <v>0.43627834245504293</v>
-      </c>
-      <c r="H52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.46657571623465222</v>
-      </c>
-      <c r="I52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.31671732522796359</v>
-      </c>
-      <c r="J52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.27336860670194008</v>
-      </c>
-      <c r="K52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.24550898203592819</v>
-      </c>
-      <c r="L52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.21302325581395354</v>
-      </c>
-      <c r="M52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.28808864265927969</v>
-      </c>
-      <c r="N52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.31486611265004627</v>
-      </c>
-      <c r="O52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.15297202797202791</v>
-      </c>
-      <c r="P52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.16794478527607359</v>
-      </c>
-      <c r="Q52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.24551971326164868</v>
-      </c>
-      <c r="R52" s="5">
-        <f t="shared" si="86"/>
-        <v>0.1836376404494382</v>
-      </c>
-      <c r="S52" s="5">
-        <f t="shared" si="86"/>
         <v>0.41963608794541329</v>
       </c>
-      <c r="T52" s="5">
+      <c r="T54" s="14">
         <f>T12/P12-1</f>
         <v>0.50393959290873269</v>
       </c>
-      <c r="AB52" s="12"/>
-      <c r="AC52" s="12">
-        <f t="shared" ref="AC52:AK52" si="87">AC12/AB12-1</f>
+      <c r="AB54" s="13"/>
+      <c r="AC54" s="13">
+        <f t="shared" ref="AC54:AK54" si="85">AC12/AB12-1</f>
         <v>0.36578558528977179</v>
       </c>
-      <c r="AD52" s="12">
+      <c r="AD54" s="13">
+        <f t="shared" si="85"/>
+        <v>0.26625796369755972</v>
+      </c>
+      <c r="AE54" s="13">
+        <f t="shared" si="85"/>
+        <v>0.18948167837478636</v>
+      </c>
+      <c r="AF54" s="13">
+        <f t="shared" si="85"/>
+        <v>0.29280925778132483</v>
+      </c>
+      <c r="AG54" s="13">
+        <f t="shared" si="85"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AH54" s="13">
+        <f t="shared" si="85"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AI54" s="13">
+        <f t="shared" si="85"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AJ54" s="13">
+        <f t="shared" si="85"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AK54" s="13">
+        <f t="shared" si="85"/>
+        <v>0.14999999999999991</v>
+      </c>
+    </row>
+    <row r="55" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G55" s="14">
+        <f t="shared" ref="G55:T55" si="86">G11/C11-1</f>
+        <v>1.4821428571428572</v>
+      </c>
+      <c r="H55" s="14">
+        <f t="shared" si="86"/>
+        <v>0.7424942263279446</v>
+      </c>
+      <c r="I55" s="14">
+        <f t="shared" si="86"/>
+        <v>0.39570277529095788</v>
+      </c>
+      <c r="J55" s="14">
+        <f t="shared" si="86"/>
+        <v>9.7709923664122122E-2</v>
+      </c>
+      <c r="K55" s="14">
+        <f t="shared" si="86"/>
+        <v>6.9326357096141322E-2</v>
+      </c>
+      <c r="L55" s="14">
+        <f t="shared" si="86"/>
+        <v>0.99734923790589791</v>
+      </c>
+      <c r="M55" s="14">
+        <f t="shared" si="86"/>
+        <v>0.52405388069275172</v>
+      </c>
+      <c r="N55" s="14">
+        <f t="shared" si="86"/>
+        <v>1.1286509040333796</v>
+      </c>
+      <c r="O55" s="14">
+        <f t="shared" si="86"/>
+        <v>0.66972477064220182</v>
+      </c>
+      <c r="P55" s="14">
+        <f t="shared" si="86"/>
+        <v>-7.4651625746516292E-2</v>
+      </c>
+      <c r="Q55" s="14">
+        <f t="shared" si="86"/>
+        <v>0.43728956228956228</v>
+      </c>
+      <c r="R55" s="14">
+        <f t="shared" si="86"/>
+        <v>0.25351192420777524</v>
+      </c>
+      <c r="S55" s="14">
+        <f t="shared" si="86"/>
+        <v>-0.11794871794871797</v>
+      </c>
+      <c r="T55" s="14">
+        <f t="shared" si="86"/>
+        <v>0.12549300824668341</v>
+      </c>
+      <c r="AB55" s="13"/>
+      <c r="AC55" s="13">
+        <f t="shared" ref="AC55:AK55" si="87">AC11/AB11-1</f>
+        <v>0.54387311332821686</v>
+      </c>
+      <c r="AD55" s="13">
         <f t="shared" si="87"/>
-        <v>0.26625796369755972</v>
-      </c>
-      <c r="AE52" s="12">
+        <v>0.67125103562551791</v>
+      </c>
+      <c r="AE55" s="13">
         <f t="shared" si="87"/>
-        <v>0.18948167837478636</v>
-      </c>
-      <c r="AF52" s="12">
+        <v>0.26621058893515759</v>
+      </c>
+      <c r="AF55" s="13">
         <f t="shared" si="87"/>
-        <v>0.29280925778132483</v>
-      </c>
-      <c r="AG52" s="12">
+        <v>8.7369822253543061E-2</v>
+      </c>
+      <c r="AG55" s="13">
         <f t="shared" si="87"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AH52" s="12">
+        <v>0.14999999999999969</v>
+      </c>
+      <c r="AH55" s="13">
         <f t="shared" si="87"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AI52" s="12">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AI55" s="13">
         <f t="shared" si="87"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AJ52" s="12">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AJ55" s="13">
         <f t="shared" si="87"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AK52" s="12">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AK55" s="13">
         <f t="shared" si="87"/>
-        <v>0.14999999999999991</v>
+        <v>0.10000000000000009</v>
       </c>
     </row>
-    <row r="53" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G53" s="5">
-        <f t="shared" ref="G53:T53" si="88">G11/C11-1</f>
-        <v>1.4821428571428572</v>
-      </c>
-      <c r="H53" s="5">
+    <row r="56" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G56" s="14">
+        <f t="shared" ref="G56:S56" si="88">G13/C13-1</f>
+        <v>0.24381531243335464</v>
+      </c>
+      <c r="H56" s="14">
         <f t="shared" si="88"/>
-        <v>0.7424942263279446</v>
-      </c>
-      <c r="I53" s="5">
+        <v>0.47200897602456604</v>
+      </c>
+      <c r="I56" s="14">
         <f t="shared" si="88"/>
-        <v>0.39570277529095788</v>
-      </c>
-      <c r="J53" s="5">
+        <v>8.8375128181224838E-2</v>
+      </c>
+      <c r="J56" s="14">
         <f t="shared" si="88"/>
-        <v>9.7709923664122122E-2</v>
-      </c>
-      <c r="K53" s="5">
+        <v>3.4912410560078877E-2</v>
+      </c>
+      <c r="K56" s="14">
         <f t="shared" si="88"/>
-        <v>6.9326357096141322E-2</v>
-      </c>
-      <c r="L53" s="5">
+        <v>-8.6930429936988296E-2</v>
+      </c>
+      <c r="L56" s="14">
         <f t="shared" si="88"/>
-        <v>0.99734923790589791</v>
-      </c>
-      <c r="M53" s="5">
+        <v>2.2987122397400306E-2</v>
+      </c>
+      <c r="M56" s="14">
         <f t="shared" si="88"/>
-        <v>0.52405388069275172</v>
-      </c>
-      <c r="N53" s="5">
+        <v>7.8458244111349051E-2</v>
+      </c>
+      <c r="N56" s="14">
         <f t="shared" si="88"/>
-        <v>1.1286509040333796</v>
-      </c>
-      <c r="O53" s="5">
+        <v>2.1456669448086885E-2</v>
+      </c>
+      <c r="O56" s="14">
         <f t="shared" si="88"/>
-        <v>0.66972477064220182</v>
-      </c>
-      <c r="P53" s="5">
+        <v>-9.2296136331627587E-2</v>
+      </c>
+      <c r="P56" s="14">
         <f t="shared" si="88"/>
-        <v>-7.4651625746516292E-2</v>
-      </c>
-      <c r="Q53" s="5">
+        <v>-0.1178039215686274</v>
+      </c>
+      <c r="Q56" s="14">
         <f t="shared" si="88"/>
-        <v>0.43728956228956228</v>
-      </c>
-      <c r="R53" s="5">
+        <v>0.11567786514176803</v>
+      </c>
+      <c r="R56" s="14">
         <f t="shared" si="88"/>
-        <v>0.25351192420777524</v>
-      </c>
-      <c r="S53" s="5">
+        <v>-3.1353327887345905E-2</v>
+      </c>
+      <c r="S56" s="14">
         <f t="shared" si="88"/>
-        <v>-0.11794871794871797</v>
-      </c>
-      <c r="T53" s="5">
-        <f t="shared" si="88"/>
-        <v>0.12549300824668341</v>
-      </c>
-      <c r="AB53" s="12"/>
-      <c r="AC53" s="12">
-        <f t="shared" ref="AC53:AK53" si="89">AC11/AB11-1</f>
-        <v>0.54387311332821686</v>
-      </c>
-      <c r="AD53" s="12">
-        <f t="shared" si="89"/>
-        <v>0.67125103562551791</v>
-      </c>
-      <c r="AE53" s="12">
-        <f t="shared" si="89"/>
-        <v>0.26621058893515759</v>
-      </c>
-      <c r="AF53" s="12">
-        <f t="shared" si="89"/>
-        <v>8.7369822253543061E-2</v>
-      </c>
-      <c r="AG53" s="12">
-        <f t="shared" si="89"/>
-        <v>0.14999999999999969</v>
-      </c>
-      <c r="AH53" s="12">
-        <f t="shared" si="89"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AI53" s="12">
-        <f t="shared" si="89"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AJ53" s="12">
-        <f t="shared" si="89"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AK53" s="12">
-        <f t="shared" si="89"/>
-        <v>0.10000000000000009</v>
-      </c>
-    </row>
-    <row r="54" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G54" s="5">
-        <f t="shared" ref="G54:S54" si="90">G13/C13-1</f>
-        <v>0.24381531243335464</v>
-      </c>
-      <c r="H54" s="5">
-        <f t="shared" si="90"/>
-        <v>0.47200897602456604</v>
-      </c>
-      <c r="I54" s="5">
-        <f t="shared" si="90"/>
-        <v>8.8375128181224838E-2</v>
-      </c>
-      <c r="J54" s="5">
-        <f t="shared" si="90"/>
-        <v>3.4912410560078877E-2</v>
-      </c>
-      <c r="K54" s="5">
-        <f t="shared" si="90"/>
-        <v>-8.6930429936988296E-2</v>
-      </c>
-      <c r="L54" s="5">
-        <f t="shared" si="90"/>
-        <v>2.2987122397400306E-2</v>
-      </c>
-      <c r="M54" s="5">
-        <f t="shared" si="90"/>
-        <v>7.8458244111349051E-2</v>
-      </c>
-      <c r="N54" s="5">
-        <f t="shared" si="90"/>
-        <v>2.1456669448086885E-2</v>
-      </c>
-      <c r="O54" s="5">
-        <f t="shared" si="90"/>
-        <v>-9.2296136331627587E-2</v>
-      </c>
-      <c r="P54" s="5">
-        <f t="shared" si="90"/>
-        <v>-0.1178039215686274</v>
-      </c>
-      <c r="Q54" s="5">
-        <f t="shared" si="90"/>
-        <v>0.11567786514176803</v>
-      </c>
-      <c r="R54" s="5">
-        <f t="shared" si="90"/>
-        <v>-3.1353327887345905E-2</v>
-      </c>
-      <c r="S54" s="5">
-        <f t="shared" si="90"/>
         <v>0.15784846133953967</v>
       </c>
-      <c r="T54" s="5">
+      <c r="T56" s="14">
         <f>T13/P13-1</f>
         <v>0.25515647226173543</v>
       </c>
-      <c r="AB54" s="12"/>
-      <c r="AC54" s="12">
-        <f t="shared" ref="AC54:AK54" si="91">AC13/AB13-1</f>
+      <c r="AB56" s="13"/>
+      <c r="AC56" s="13">
+        <f t="shared" ref="AC56:AK56" si="89">AC13/AB13-1</f>
         <v>0.18795266504627928</v>
       </c>
-      <c r="AD54" s="12">
+      <c r="AD56" s="13">
+        <f t="shared" si="89"/>
+        <v>9.4757835346634955E-3</v>
+      </c>
+      <c r="AE56" s="13">
+        <f t="shared" si="89"/>
+        <v>-2.9306991503736279E-2</v>
+      </c>
+      <c r="AF56" s="13">
+        <f t="shared" si="89"/>
+        <v>0.11271262404167603</v>
+      </c>
+      <c r="AG56" s="13">
+        <f t="shared" si="89"/>
+        <v>4.484050639149606E-2</v>
+      </c>
+      <c r="AH56" s="13">
+        <f t="shared" si="89"/>
+        <v>-0.21136442766851082</v>
+      </c>
+      <c r="AI56" s="13">
+        <f t="shared" si="89"/>
+        <v>0.59626355270563569</v>
+      </c>
+      <c r="AJ56" s="13">
+        <f t="shared" si="89"/>
+        <v>0.47915981934935048</v>
+      </c>
+      <c r="AK56" s="13">
+        <f t="shared" si="89"/>
+        <v>0.34409499138351918</v>
+      </c>
+    </row>
+    <row r="57" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="14">
+        <f t="shared" ref="C57:T57" si="90">C19/C13</f>
+        <v>0.29110684580934099</v>
+      </c>
+      <c r="D57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.25002952639659853</v>
+      </c>
+      <c r="E57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.25086231005873033</v>
+      </c>
+      <c r="F57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.23756065465910026</v>
+      </c>
+      <c r="G57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.19336448197522396</v>
+      </c>
+      <c r="H57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.18185100493440848</v>
+      </c>
+      <c r="I57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.17892933618843684</v>
+      </c>
+      <c r="J57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.17634203520483172</v>
+      </c>
+      <c r="K57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.1735129806112389</v>
+      </c>
+      <c r="L57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.17952941176470588</v>
+      </c>
+      <c r="M57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.19843539035819235</v>
+      </c>
+      <c r="N57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.16256272610572994</v>
+      </c>
+      <c r="O57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.16307214895267649</v>
+      </c>
+      <c r="P57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.17238620199146515</v>
+      </c>
+      <c r="Q57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.1798896600818651</v>
+      </c>
+      <c r="R57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.20115658005702583</v>
+      </c>
+      <c r="S57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.21083664626792334</v>
+      </c>
+      <c r="T57" s="14">
+        <f t="shared" si="90"/>
+        <v>0.16826037682391273</v>
+      </c>
+      <c r="AB57" s="13">
+        <f t="shared" ref="AB57:AK57" si="91">AB19/AB13</f>
+        <v>0.25598438535759005</v>
+      </c>
+      <c r="AC57" s="13">
         <f t="shared" si="91"/>
-        <v>9.4757835346634955E-3</v>
-      </c>
-      <c r="AE54" s="12">
+        <v>0.18248891736331416</v>
+      </c>
+      <c r="AD57" s="13">
         <f t="shared" si="91"/>
-        <v>-2.9306991503736279E-2</v>
-      </c>
-      <c r="AF54" s="12">
+        <v>0.17862626676220697</v>
+      </c>
+      <c r="AE57" s="13">
         <f t="shared" si="91"/>
-        <v>0.11271262404167603</v>
-      </c>
-      <c r="AG54" s="12">
+        <v>0.18026511436616155</v>
+      </c>
+      <c r="AF57" s="13">
         <f t="shared" si="91"/>
-        <v>4.484050639149606E-2</v>
-      </c>
-      <c r="AH54" s="12">
+        <v>0.19285939313537168</v>
+      </c>
+      <c r="AG57" s="13">
         <f t="shared" si="91"/>
-        <v>-0.21136442766851082</v>
-      </c>
-      <c r="AI54" s="12">
+        <v>0.19513081571158658</v>
+      </c>
+      <c r="AH57" s="13">
         <f t="shared" si="91"/>
-        <v>0.59626355270563569</v>
-      </c>
-      <c r="AJ54" s="12">
+        <v>0.19572680145027493</v>
+      </c>
+      <c r="AI57" s="13">
         <f t="shared" si="91"/>
-        <v>0.47915981934935048</v>
-      </c>
-      <c r="AK54" s="12">
+        <v>0.23209344117104364</v>
+      </c>
+      <c r="AJ57" s="13">
         <f t="shared" si="91"/>
-        <v>0.34409499138351918</v>
+        <v>0.2140797310035506</v>
+      </c>
+      <c r="AK57" s="13">
+        <f t="shared" si="91"/>
+        <v>0.20281960677720395</v>
       </c>
     </row>
-    <row r="55" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" s="5">
-        <f t="shared" ref="C55:T55" si="92">C19/C13</f>
-        <v>0.29110684580934099</v>
-      </c>
-      <c r="D55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.25002952639659853</v>
-      </c>
-      <c r="E55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.25086231005873033</v>
-      </c>
-      <c r="F55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.23756065465910026</v>
-      </c>
-      <c r="G55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.19336448197522396</v>
-      </c>
-      <c r="H55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.18185100493440848</v>
-      </c>
-      <c r="I55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.17892933618843684</v>
-      </c>
-      <c r="J55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.17634203520483172</v>
-      </c>
-      <c r="K55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.1735129806112389</v>
-      </c>
-      <c r="L55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.17952941176470588</v>
-      </c>
-      <c r="M55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.19843539035819235</v>
-      </c>
-      <c r="N55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.16256272610572994</v>
-      </c>
-      <c r="O55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.16307214895267649</v>
-      </c>
-      <c r="P55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.17238620199146515</v>
-      </c>
-      <c r="Q55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.1798896600818651</v>
-      </c>
-      <c r="R55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.20115658005702583</v>
-      </c>
-      <c r="S55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.21083664626792334</v>
-      </c>
-      <c r="T55" s="5">
-        <f t="shared" si="92"/>
-        <v>0.16826037682391273</v>
-      </c>
-      <c r="AB55" s="12">
-        <f t="shared" ref="AB55:AK55" si="93">AB19/AB13</f>
-        <v>0.25598438535759005</v>
-      </c>
-      <c r="AC55" s="12">
-        <f t="shared" si="93"/>
-        <v>0.18248891736331416</v>
-      </c>
-      <c r="AD55" s="12">
-        <f t="shared" si="93"/>
-        <v>0.17862626676220697</v>
-      </c>
-      <c r="AE55" s="12">
-        <f t="shared" si="93"/>
-        <v>0.18026511436616155</v>
-      </c>
-      <c r="AF55" s="12">
-        <f t="shared" si="93"/>
-        <v>0.19285939313537168</v>
-      </c>
-      <c r="AG55" s="12">
-        <f t="shared" si="93"/>
-        <v>0.19513081571158658</v>
-      </c>
-      <c r="AH55" s="12">
-        <f t="shared" si="93"/>
-        <v>0.19572680145027493</v>
-      </c>
-      <c r="AI55" s="12">
-        <f t="shared" si="93"/>
-        <v>0.23209344117104364</v>
-      </c>
-      <c r="AJ55" s="12">
-        <f t="shared" si="93"/>
-        <v>0.2140797310035506</v>
-      </c>
-      <c r="AK55" s="12">
-        <f t="shared" si="93"/>
-        <v>0.20281960677720395</v>
+    <row r="59" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="15" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="57" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B57" s="6" t="s">
-        <v>57</v>
+    <row r="60" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="16" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="58" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B58" s="6" t="s">
-        <v>58</v>
+    <row r="65" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" s="2" t="s">
-        <v>68</v>
+    <row r="71" spans="2:2" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B71" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="69" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B69" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="B70" s="8" t="s">
+    <row r="72" spans="2:2" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="B72" s="10" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A38:A40"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <drawing r:id="rId1"/>
